--- a/docs/xlsx/jobs-2026-10-19.xlsx
+++ b/docs/xlsx/jobs-2026-10-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="669">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1996 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>2027 Horticulture Apprentice</t>
+  </si>
+  <si>
+    <t>Oak Spring Garden Foundation</t>
+  </si>
+  <si>
+    <t>Upperville, VA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$20 per hour</t>
+  </si>
+  <si>
+    <t>botany</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-2027-horticulture-apprentice-upperville-virginia/6118058362</t>
+  </si>
+  <si>
+    <t>Biological Science Technician (Aquatics/Fisheries)</t>
+  </si>
+  <si>
+    <t>National Park Service</t>
+  </si>
+  <si>
+    <t>Three Rivers, CA</t>
+  </si>
+  <si>
+    <t>$17.45 - $21.87 per hour</t>
+  </si>
+  <si>
+    <t>fisheries-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-biological-science-technician-aquaticsfisheries-three-rivers-california/6229692300</t>
+  </si>
+  <si>
+    <t>Canvass Director</t>
+  </si>
+  <si>
+    <t>Fund for the Public Interest</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>The target annual compensation for this position is $40,000-$53,750, depending on position and location.</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-director-washington-dc/3771808085</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-director-oakland-california/5215538271</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>The target annual compensation for this position is $40,000-$53,750, depending on position and location</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-director-seattle-washington/3237113329</t>
+  </si>
+  <si>
+    <t>Denver, CO</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-director-denver-colorado/8129306233</t>
+  </si>
+  <si>
+    <t>Santa Cruz, CA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-director-santa-cruz-california/7617719196</t>
+  </si>
+  <si>
+    <t>Chief Program Officer</t>
+  </si>
+  <si>
+    <t>DarkSky International</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>$138,000 - $161,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-chief-program-officer-remote-remote/7625259683</t>
+  </si>
+  <si>
+    <t>Clean Water and Conservation Organizer</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Philadelphia, PA</t>
+  </si>
+  <si>
+    <t>The target annual compensation for this entry level position is $40,000 in the first year.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-clean-water-and-conservation-organizer-philadelphia-pennsylvania/2749361103</t>
+  </si>
+  <si>
+    <t>Conservation and Grants Manager</t>
+  </si>
+  <si>
+    <t>Unique Places to Save</t>
+  </si>
+  <si>
+    <t>Central or Western, NC</t>
+  </si>
+  <si>
+    <t>$60,000 - $70,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-and-grants-manager-central-or-western-north-carolina/4796987770</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>Tillamook Estuaries Partnership</t>
+  </si>
+  <si>
+    <t>Garibaldi, OR</t>
+  </si>
+  <si>
+    <t>$60,300 - $71,900 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-development-coordinator-garibaldi-oregon/3647388500</t>
+  </si>
+  <si>
+    <t>Director-Wyoming Game and Fish Department</t>
+  </si>
+  <si>
+    <t>Wyoming Game &amp; Fish</t>
+  </si>
+  <si>
+    <t>Cheyenne, WY</t>
+  </si>
+  <si>
+    <t>$14,279.20 - $15,866.93 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-wyoming-game-and-fish-department-cheyenne-wyoming/6235402506</t>
+  </si>
+  <si>
+    <t>EPA Biology Research Opportunity on the Aquatic Toxicity and Bioaccumulation of PFAS</t>
+  </si>
+  <si>
+    <t>U.S. Environmental Protection Agency (EPA)</t>
+  </si>
+  <si>
+    <t>Duluth, MN</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>Stipend $50,460.00 Yearly</t>
+  </si>
+  <si>
+    <t>ecology-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-epa-biology-research-opportunity-on-the-aquatic-toxicity-and-bioaccumulation-of-pfas-duluth-minnesota/3635580455</t>
+  </si>
+  <si>
+    <t>Executive Coordinator</t>
+  </si>
+  <si>
+    <t>Centennial Valley Association</t>
+  </si>
+  <si>
+    <t>Lima, MT</t>
+  </si>
+  <si>
+    <t>$52,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-coordinator-lima-montana/2639835185</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Henry L Ferguson Museum</t>
+  </si>
+  <si>
+    <t>Fishers Island, CT</t>
+  </si>
+  <si>
+    <t>$110,000 - $150,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-fishers-island-connecticut/1024468534</t>
+  </si>
+  <si>
+    <t>The Pisgah Conservancy</t>
+  </si>
+  <si>
+    <t>Brevard, NC</t>
+  </si>
+  <si>
+    <t>$115,000 - $135,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-brevard-north-carolina/5199432092</t>
+  </si>
+  <si>
+    <t>Executive Director, Compost Research &amp; Education Foundation (CREF)</t>
+  </si>
+  <si>
+    <t>Compost Research &amp; Education Foundation</t>
+  </si>
+  <si>
+    <t>Raleigh, NC</t>
+  </si>
+  <si>
+    <t>$75,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-compost-research--education-foundation-cref-raleigh-north-carolina/9490018273</t>
+  </si>
+  <si>
+    <t>Facilities Maintenance Supervisor</t>
+  </si>
+  <si>
+    <t>Kansas Department of Wildlife and Parks</t>
+  </si>
+  <si>
+    <t>Manhattan, KS</t>
+  </si>
+  <si>
+    <t>$22.81 - $23.71 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-facilities-maintenance-supervisor-manhattan-kansas/5496283638</t>
+  </si>
+  <si>
+    <t>Fellow</t>
+  </si>
+  <si>
+    <t>Emerging Leaders for Climate Action</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fellow-washington-dc/8518143786</t>
+  </si>
+  <si>
+    <t>Field Technician</t>
+  </si>
+  <si>
+    <t>Southeastern Grasslands Institute at Austin Peay State University</t>
+  </si>
+  <si>
+    <t>Clarksville, TN</t>
+  </si>
+  <si>
+    <t>$40,000 per year</t>
+  </si>
+  <si>
+    <t>botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-technician-clarksville-tennessee/3221762938</t>
+  </si>
+  <si>
+    <t>HCRI Marine Pelagic Species Specialist (RCUH ID# 226642)</t>
+  </si>
+  <si>
+    <t>Hawaiʻi Coral Reef Initiative (HCRI) / Research Corporation of the University of Hawaiʻi (RCUH)</t>
+  </si>
+  <si>
+    <t>Kona, HI</t>
+  </si>
+  <si>
+    <t>$5,150 per month</t>
+  </si>
+  <si>
+    <t>marine-biology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-hcri-marine-pelagic-species-specialist-rcuh-id-226642-kona-hawaii/9008229751</t>
+  </si>
+  <si>
+    <t>Land Conservation Manager</t>
+  </si>
+  <si>
+    <t>New Mexico Land Conservancy</t>
+  </si>
+  <si>
+    <t>Santa Fe, NM</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-land-conservation-manager-santa-fe-new-mexico/8093019779</t>
+  </si>
+  <si>
+    <t>Officer of Risk and Safety Management</t>
+  </si>
+  <si>
+    <t>The Student Conservation Association</t>
+  </si>
+  <si>
+    <t>$70,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-officer-of-risk-and-safety-management-remote-remote/6701316089</t>
+  </si>
+  <si>
+    <t>Public Interest Advocate</t>
+  </si>
+  <si>
+    <t>PIRG</t>
+  </si>
+  <si>
+    <t>Boise, ID</t>
+  </si>
+  <si>
+    <t>The starting target annual compensation range for someone with 4-8 years of relevant experience is $43,500-$60,000.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-public-interest-advocate-boise-idaho/4922680836</t>
+  </si>
+  <si>
+    <t>Public Outreach &amp; Recreation Assistant at Ottawa National Forest</t>
+  </si>
+  <si>
+    <t>Wisconsin Conservation Corps</t>
+  </si>
+  <si>
+    <t>Watersmeet, MI</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$500 per week</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-public-outreach--recreation-assistant-at-ottawa-national-forest-watersmeet-michigan/6324323136</t>
+  </si>
+  <si>
+    <t>Regional Technical Assistance Manager</t>
+  </si>
+  <si>
+    <t>Idaho Department of Fish and Game</t>
+  </si>
+  <si>
+    <t>Lewiston, ID</t>
+  </si>
+  <si>
+    <t>$32.97 - $41.21 per hour</t>
+  </si>
+  <si>
+    <t>fisheries-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-regional-technical-assistance-manager-lewiston-idaho/8347471561</t>
+  </si>
+  <si>
+    <t>Research Associate I (Partner Coordinator)</t>
+  </si>
+  <si>
+    <t>University of Illinois Chicago</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>$49,000 - $55,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-research-associate-i-partner-coordinator-chicago-illinois/4389245097</t>
+  </si>
+  <si>
+    <t>Resource Compliance Technician</t>
+  </si>
+  <si>
+    <t>Landhawk Consulting</t>
+  </si>
+  <si>
+    <t>El Paso, TX</t>
+  </si>
+  <si>
+    <t>$16.25 - $30 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-resource-compliance-technician-el-paso-texas/7466292726</t>
+  </si>
+  <si>
+    <t>Restoration Field Specialist</t>
+  </si>
+  <si>
+    <t>Huron Pines</t>
+  </si>
+  <si>
+    <t>Alpena, MI</t>
+  </si>
+  <si>
+    <t>$25 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-restoration-field-specialist-alpena-michigan/9506656463</t>
+  </si>
+  <si>
+    <t>Seafood Business and Market Development Specialist</t>
+  </si>
+  <si>
+    <t>North Carolina Sea Grant</t>
+  </si>
+  <si>
+    <t>Morehead City, NC</t>
+  </si>
+  <si>
+    <t>$70,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>sustainability-admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-seafood-business-and-market-development-specialist-morehead-city-north-carolina/1895437537</t>
+  </si>
+  <si>
+    <t>Sierra Nevada Yellow-Legged Frog Project Manager</t>
+  </si>
+  <si>
+    <t>Plumas Audubon Society</t>
+  </si>
+  <si>
+    <t>Quincy, CA</t>
+  </si>
+  <si>
+    <t>$25 - $30 per hour</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sierra-nevada-yellow-legged-frog-project-manager-quincy-california/7452067962</t>
+  </si>
+  <si>
+    <t>Teacher Naturalist</t>
+  </si>
+  <si>
+    <t>Great Smoky Mountains Institute at Tremont</t>
+  </si>
+  <si>
+    <t>Townsend, TN</t>
+  </si>
+  <si>
+    <t>$425 per week</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-teacher-naturalist-townsend-tennessee/3459653036</t>
+  </si>
+  <si>
+    <t>Trails Technician</t>
+  </si>
+  <si>
+    <t>Laguna Canyon Foundation</t>
+  </si>
+  <si>
+    <t>Laguna Beach, CA</t>
+  </si>
+  <si>
+    <t>$21 - $22 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-trails-technician-laguna-beach-california/7577254832</t>
+  </si>
+  <si>
+    <t>USDA ARS Data Analytics and Plant Genetics Fellowship</t>
+  </si>
+  <si>
+    <t>U.S. Department of Agriculture (USDA)</t>
+  </si>
+  <si>
+    <t>Urbana, IL</t>
+  </si>
+  <si>
+    <t>Stipend $70,000.00 – $90,000.00 Yearly</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-ars-data-analytics-and-plant-genetics-fellowship-urbana-illinois/4051739385</t>
+  </si>
+  <si>
+    <t>USDA-FS Fellowship for Preparation and Analysis of Environmental Samples</t>
+  </si>
+  <si>
+    <t>Grand Rapids, MN</t>
+  </si>
+  <si>
+    <t>Stipend $680.00 – $1,360.00 Monthly</t>
+  </si>
+  <si>
+    <t>ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-fs-fellowship-for-preparation-and-analysis-of-environmental-samples-grand-rapids-minnesota/1891019219</t>
+  </si>
+  <si>
+    <t>Warehouse Operator 1 or 2</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$3,653 - $4,406 per month</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-warehouse-operator-1-or-2-olympia-washington/5612663567</t>
+  </si>
+  <si>
+    <t>Wildlife Health Coordinator - Environmental Scientist III</t>
+  </si>
+  <si>
+    <t>Delaware Division of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Greenwood, DE</t>
+  </si>
+  <si>
+    <t>$58,302 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-health-coordinator---environmental-scientist-iii-greenwood-delaware/4573582810</t>
+  </si>
+  <si>
+    <t>Field Crew Leader (Backcountry, Forestry, Fuels, Trails)</t>
+  </si>
+  <si>
+    <t>Montana Conservation Corps</t>
+  </si>
+  <si>
+    <t>Bozeman, Montana, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>Less than 20,000</t>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/field-crew-leader-backcountry-forestry-fuels-trails/</t>
+  </si>
+  <si>
+    <t>Wildland Restoration Team Leader</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/wildland-restoration-team-leader/</t>
+  </si>
+  <si>
+    <t>Youth Crew Leader</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/youth-crew-leader-2/</t>
+  </si>
+  <si>
+    <t>Advancement Director, Mid-Atlantic</t>
+  </si>
+  <si>
+    <t>Parkinson's Foundation</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/97cce89512464d7ebd3ab360eb6a7fcf-advancement-director-mid-atlantic-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>AgriSea Sales and Operations Associate</t>
+  </si>
+  <si>
+    <t>GreenWave</t>
+  </si>
+  <si>
+    <t>New Haven, Connecticut</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Agriculture, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2b4e04e97522463eb846efc9749565b7-agrisea-sales-and-operations-associate-greenwave-new-haven</t>
+  </si>
+  <si>
+    <t>Assistant Executive Director of Annual Giving</t>
+  </si>
+  <si>
+    <t>St. Mary's University of San Antonio</t>
+  </si>
+  <si>
+    <t>San Antonio, Texas</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a8ba154c1264176976dae7aef51c51b-assistant-executive-director-of-annual-giving-st-marys-university-of-san-antonio-san-antonio</t>
+  </si>
+  <si>
+    <t>Assistente Jr de Captação de Recursos</t>
+  </si>
+  <si>
+    <t>Instituto Jose Zimerman</t>
+  </si>
+  <si>
+    <t>Taboão da Serra, Estado de São Paulo, BR</t>
+  </si>
+  <si>
+    <t>RSD 2500.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f8967a575bad47819d8d0425d598ab42-assistente-jr-de-captacao-de-recursos-instituto-jose-zimerman-taboao-da-serra</t>
+  </si>
+  <si>
+    <t>Associate Editor</t>
+  </si>
+  <si>
+    <t>Real Change Homeless Empowerment Project</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Human Rights Civil Liberties, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d3dda57481e24b959f755daaeba60f42-associate-editor-real-change-homeless-empowerment-project-seattle</t>
+  </si>
+  <si>
+    <t>Athletics Assistant</t>
+  </si>
+  <si>
+    <t>Variety Boys &amp; Girls Club</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3eda6db76a5447a88d1000b5736820ba-athletics-assistant-variety-boys-girls-club-los-angeles</t>
+  </si>
+  <si>
+    <t>Attorney: Represent New York State in Court of Claims (3919)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>Buffalo, New York</t>
+  </si>
+  <si>
+    <t>USD 87356.00 - 186494.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/6c45c7a4d0d14e1f8b488e9bfada2112-attorney-represent-new-york-state-in-court-of-claims-3919-new-york-state-office-of-the-attorney-general-buffalo</t>
+  </si>
+  <si>
+    <t>Bi-Lingual Case Manager</t>
+  </si>
+  <si>
+    <t>Coalition for the Homeless</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/745d059fc6ae42f8b54e74fae3e4e9fa-bi-lingual-case-manager-coalition-for-the-homeless-new-york</t>
+  </si>
+  <si>
+    <t>Bilingual Social Worker</t>
+  </si>
+  <si>
+    <t>Central Union Mission</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/582bd885fa664d1d9df44f84709db92e-bilingual-social-worker-central-union-mission-arlington</t>
+  </si>
+  <si>
+    <t>Board Members (Multiple Seats: Mon Valley Resident Seats and At Large Seats)</t>
+  </si>
+  <si>
+    <t>Valley Clean Air Now</t>
+  </si>
+  <si>
+    <t>Remote (Pennsylvania)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d530b8be5c84846b57fe7b2947af867-board-members-multiple-seats-mon-valley-resident-seats-and-at-large-seats-valley-clean-air-now-glassport</t>
+  </si>
+  <si>
+    <t>Career Coach</t>
+  </si>
+  <si>
+    <t>Wanderlust Careers</t>
+  </si>
+  <si>
+    <t>USD 40.00/hour</t>
+  </si>
+  <si>
+    <t>Job Workplace, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/52939455a6ab44fb88b4de3e2b3afa41-career-coach-wanderlust-careers-new-york</t>
+  </si>
+  <si>
+    <t>Case Manager - Bedford</t>
+  </si>
+  <si>
+    <t>Geel Community Services, Inc.</t>
+  </si>
+  <si>
+    <t>The Bronx, New York</t>
+  </si>
+  <si>
+    <t>USD 56774.00 - 56774.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cbb7629c51564eadaa7e0cea54bc09b8-case-manager-bedford-geel-community-services-inc-the-bronx</t>
+  </si>
+  <si>
+    <t>Case Manager (Grand Ave Studios)</t>
+  </si>
+  <si>
+    <t>USD 63052.17 - 63052.17/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Disability, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fed1bfe3bee34d12b57ad4186a59c8b2-case-manager-grand-ave-studios-geel-community-services-inc-the-bronx</t>
+  </si>
+  <si>
+    <t>Chief Operations Officer</t>
+  </si>
+  <si>
+    <t>Oregon State Bar</t>
+  </si>
+  <si>
+    <t>Tigard, OR</t>
+  </si>
+  <si>
+    <t>USD 162361.25 - 202951.60/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37da75dc627a42c4b9f938fa5ee9c13e-chief-operations-officer-oregon-state-bar-tigard</t>
+  </si>
+  <si>
+    <t>Clinical Operations Director</t>
+  </si>
+  <si>
+    <t>Community Health Services</t>
+  </si>
+  <si>
+    <t>Aspen, Colorado</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Reproductive Health Rights, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/449c023eafab47188a800be1c83f60f2-clinical-operations-director-community-health-services-aspen</t>
+  </si>
+  <si>
+    <t>Communications and Events Manager</t>
+  </si>
+  <si>
+    <t>West End House</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 64500.00 - 71000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aefc2e7c64974584a986e65592b75b51-communications-and-events-manager-west-end-house-boston</t>
+  </si>
+  <si>
+    <t>Communications Associate</t>
+  </si>
+  <si>
+    <t>Fair Elections Center</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/df38054cb3044867b25d0d41d3d84961-communications-associate-fair-elections-center-washington</t>
+  </si>
+  <si>
+    <t>Construction Instructional Coordinator</t>
+  </si>
+  <si>
+    <t>Texas Climate Jobs Project</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>USD 65000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/686c01f01c754068a4e92a447ea08bc8-construction-instructional-coordinator-texas-climate-jobs-project-austin</t>
+  </si>
+  <si>
+    <t>Data Scientist: Use Data to Develop Legal Hypotheses (6463)</t>
+  </si>
+  <si>
+    <t>USD 120383.00 - 120383.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/19ba601216be41928e02653d0c96705b-data-scientist-use-data-to-develop-legal-hypotheses-6463-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Development and Alumni Coordinator</t>
+  </si>
+  <si>
+    <t>Alumni and Friends of Fiorello H. LaGuardia High School of Music &amp; Art and Performing Arts</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Arts Music, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c394e36c69594025833bc6f360a58dd8-development-and-alumni-coordinator-alumni-and-friends-of-fiorello-h-laguardia-high-school-of-music-art-and-performing-arts-new-york</t>
+  </si>
+  <si>
+    <t>D.C. Bar Pro Bono Center</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/56db704da5ea48acaa67e8bd41fa800d-development-coordinator-dc-bar-pro-bono-center-washington</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Hyde Square Task Force</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c21415e89c3e48579c7b33b409bfbb14-development-director-hyde-square-task-force-boston</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Seatuck Environmental Association</t>
+  </si>
+  <si>
+    <t>West Sayville, New York</t>
+  </si>
+  <si>
+    <t>Environment, Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a030a19c384845079d3682ad9ebb3c53-development-manager-seatuck-environmental-association-west-sayville</t>
+  </si>
+  <si>
+    <t>Director of Community Programs</t>
+  </si>
+  <si>
+    <t>Virginia Center for Inclusive Communities</t>
+  </si>
+  <si>
+    <t>Henrico, Virginia</t>
+  </si>
+  <si>
+    <t>USD 53550.00 - 72450.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f1c2f6fda7bd4ad68febd32f4604d38c-director-of-community-programs-virginia-center-for-inclusive-communities-henrico</t>
+  </si>
+  <si>
+    <t>Director of Development and Community Relations</t>
+  </si>
+  <si>
+    <t>ACLD</t>
+  </si>
+  <si>
+    <t>Bethpage, New York</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/427fefdd205548529c9a191d365b66b8-director-of-development-and-community-relations-acld-bethpage</t>
+  </si>
+  <si>
+    <t>Director of Institutional Giving</t>
+  </si>
+  <si>
+    <t>Bonefish &amp; Tarpon Trust</t>
+  </si>
+  <si>
+    <t>Miami, Florida</t>
+  </si>
+  <si>
+    <t>Environment, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d891e3c9488f4766898aa9e0c09fd1bd-director-of-institutional-giving-bonefish-tarpon-trust-miami</t>
+  </si>
+  <si>
+    <t>Director of Marketing</t>
+  </si>
+  <si>
+    <t>Pilots To The Rescue</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2db20a3000f457592ae281ad0a02fab-director-of-marketing-pilots-to-the-rescue-new-york</t>
+  </si>
+  <si>
+    <t>Director of Organizing and Campaigns</t>
+  </si>
+  <si>
+    <t>New Yorkers United for Child Care</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Economic Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/961423a266f645e6a024333420e7f065-director-of-organizing-and-campaigns-new-yorkers-united-for-child-care-new-york</t>
+  </si>
+  <si>
+    <t>Director of Partner Success</t>
+  </si>
+  <si>
+    <t>Credential Engine</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Job Workplace, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b5399578e0724b08b2c5db9c2158903b-director-of-partner-success-credential-engine-washington</t>
+  </si>
+  <si>
+    <t>Director of Philanthropy and Alumni Engagement</t>
+  </si>
+  <si>
+    <t>Chewonki Foundation, Inc.</t>
+  </si>
+  <si>
+    <t>Wiscasset, ME</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9df212bc9bd546ecaf3fdaaeedaf2829-director-of-philanthropy-and-alumni-engagement-chewonki-foundation-inc-wiscasset</t>
+  </si>
+  <si>
+    <t>Director of Youth Ministry</t>
+  </si>
+  <si>
+    <t>Restoration Reston Methodist Church</t>
+  </si>
+  <si>
+    <t>Reston, Virginia</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f4214be840454cfa81e17d99fc42710b-director-of-youth-ministry-restoration-reston-methodist-church-reston</t>
+  </si>
+  <si>
+    <t>Donor &amp; Member Relations Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/81aa4e6424f64dbc9d0b908083896b4c-donor-member-relations-manager-bonefish-tarpon-trust-miami</t>
+  </si>
+  <si>
+    <t>Donor Relations Associate</t>
+  </si>
+  <si>
+    <t>Harlem Academy</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a879dc819b7b4fc4a286f1449378a929-donor-relations-associate-harlem-academy-new-york</t>
+  </si>
+  <si>
+    <t>EHS CCP Disability &amp; Education Specialist</t>
+  </si>
+  <si>
+    <t>District 1199C Training &amp; Upgrading Fund</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f15bec4be7e5473b97f46fd83d07b690-ehs-ccp-disability-education-specialist-district-1199c-training-upgrading-fund-philadelphia</t>
+  </si>
+  <si>
+    <t>Events &amp; Fundraising Manager - Boston</t>
+  </si>
+  <si>
+    <t>National Ovarian Cancer Coalition - National</t>
+  </si>
+  <si>
+    <t>Remote (Boston, Massachusetts)</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/03c5477e9942489797c2e98957fc7feb-events-fundraising-manager-boston-national-ovarian-cancer-coalition-national-boston</t>
+  </si>
+  <si>
+    <t>Executive and Development Coordinator</t>
+  </si>
+  <si>
+    <t>National Park Trust</t>
+  </si>
+  <si>
+    <t>Rockville, Maryland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/058ebb02600347d0bffd433c548c7f54-executive-and-development-coordinator-national-park-trust-rockville</t>
+  </si>
+  <si>
+    <t>Executive Assistant (Part-time)</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e0bb7706ee349d4a3b149753c1d7a3c-executive-assistant-part-time-fair-elections-center-washington</t>
+  </si>
+  <si>
+    <t>Executive Assistant, Office of the President</t>
+  </si>
+  <si>
+    <t>United Way of King County (WA State)</t>
+  </si>
+  <si>
+    <t>USD 36.54 - 38.46/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b0c5821fdf7a4ed6a10896022851f4ff-executive-assistant-office-of-the-president-united-way-of-king-county-wa-state-seattle</t>
+  </si>
+  <si>
+    <t>Iroquois Center for Human Development</t>
+  </si>
+  <si>
+    <t>Greensburg, Kansas</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3092f3d57e834be980b854d653c42c0a-executive-director-iroquois-center-for-human-development-greensburg</t>
+  </si>
+  <si>
+    <t>Shifting Gears</t>
+  </si>
+  <si>
+    <t>Bellingham, Washington</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Women, Lgbtq, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/895c08444eb74157a11c27726aa9430d-executive-director-shifting-gears-bellingham</t>
+  </si>
+  <si>
+    <t>Fact-Checker</t>
+  </si>
+  <si>
+    <t>Citizens for Responsibility and Ethics in Washington</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/66ca112a788047fe82fc7c6d0ed65ea1-fact-checker-citizens-for-responsibility-and-ethics-in-washington-washington</t>
+  </si>
+  <si>
+    <t>Faculty Member in Chemisty</t>
+  </si>
+  <si>
+    <t>College of the Atlantic (COA)</t>
+  </si>
+  <si>
+    <t>Bar Harbor, Maine</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7ddc496302954eedbf61f0da86d0930d-faculty-member-in-chemisty-college-of-the-atlantic-coa-bar-harbor</t>
+  </si>
+  <si>
+    <t>Family Empowerment Advocate</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf477d80be154fcdaf6de51894d94226-family-empowerment-advocate-district-1199c-training-upgrading-fund-philadelphia</t>
+  </si>
+  <si>
+    <t>Field Coordinator - SEIU Healthcare Michigan (HCMI)</t>
+  </si>
+  <si>
+    <t>SEIU</t>
+  </si>
+  <si>
+    <t>Remote (Michigan)</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/7ca8b3605fba4aa69a105cf152f2dc1d-field-coordinator-seiu-healthcare-michigan-hcmi-seiu-detroit</t>
+  </si>
+  <si>
+    <t>Fiscal Assistant</t>
+  </si>
+  <si>
+    <t>disAbility Law Center of Virginia</t>
+  </si>
+  <si>
+    <t>Richmond, Virginia</t>
+  </si>
+  <si>
+    <t>USD 36000.00 - 49000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dda90ac1978347c09f160e9ca4d46cf2-fiscal-assistant-disability-law-center-of-virginia-richmond</t>
+  </si>
+  <si>
+    <t>General Counsel</t>
+  </si>
+  <si>
+    <t>American Rivers</t>
+  </si>
+  <si>
+    <t>Remote (Virginia)</t>
+  </si>
+  <si>
+    <t>USD 181000.00 - 250000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a28e2621857f45b780dcc359d41baab7-general-counsel-american-rivers-arlington</t>
+  </si>
+  <si>
+    <t>Grant Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Animal Charity Evaluators</t>
+  </si>
+  <si>
+    <t>USD 40.72 - 40.72/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a703582b183a4c39abcd27e5880848a6-grant-operations-coordinator-animal-charity-evaluators-covina</t>
+  </si>
+  <si>
+    <t>HIV Outreach Nurse Case Manager</t>
+  </si>
+  <si>
+    <t>Boston Health Care for the Homeless Program</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 58.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a3f6baedc0844a839495384849cff26e-hiv-outreach-nurse-case-manager-boston-health-care-for-the-homeless-program-boston</t>
+  </si>
+  <si>
+    <t>Individual Gifts Officer</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/227fd8738d844379aafcf6d251f61a3f-individual-gifts-officer-citizens-for-responsibility-and-ethics-in-washington-washington</t>
+  </si>
+  <si>
+    <t>Individual Giving &amp; Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>The Arc of Northern Virginia</t>
+  </si>
+  <si>
+    <t>Fairfax, Virginia</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/618cc506e9a146f1845b0cd45eb00663-individual-giving-engagement-coordinator-the-arc-of-northern-virginia-fairfax</t>
+  </si>
+  <si>
+    <t>Judiciary Research Manager (Court Executive 2B)</t>
+  </si>
+  <si>
+    <t>New Jersey Judiciary</t>
+  </si>
+  <si>
+    <t>Trenton, New Jersey</t>
+  </si>
+  <si>
+    <t>Job Workplace, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/650b1a7c62fb479a8e2cb903fd99f12e-judiciary-research-manager-court-executive-2b-new-jersey-judiciary-trenton</t>
+  </si>
+  <si>
+    <t>Lead Organizer - SEIU Healthcare Michigan (HCMI)</t>
+  </si>
+  <si>
+    <t>Detroit, Michigan</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/94788b17105945f7a8b2885e966c7fac-lead-organizer-seiu-healthcare-michigan-hcmi-seiu-detroit</t>
+  </si>
+  <si>
+    <t>Legal Aid Staff Attorney - Worcester</t>
+  </si>
+  <si>
+    <t>Community Legal Aid &amp; Affiliate</t>
+  </si>
+  <si>
+    <t>Worcester, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 109000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5fd5f57c37514e8c8cf28719613f3fc1-legal-aid-staff-attorney-worcester-community-legal-aid-affiliate-worcester</t>
+  </si>
+  <si>
+    <t>Legal Aid Staff Attorney (Western Mass)</t>
+  </si>
+  <si>
+    <t>Springfield, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a17a5d5b043442148bfaf183066ca8b0-legal-aid-staff-attorney-western-mass-community-legal-aid-affiliate-springfield</t>
+  </si>
+  <si>
+    <t>Litigation Supervisor, Family Defense Practice, Bronx</t>
+  </si>
+  <si>
+    <t>Center for Family Representation, Inc.</t>
+  </si>
+  <si>
+    <t>USD 120500.00 - 144700.00/year</t>
+  </si>
+  <si>
+    <t>Family, Housing Homelessness, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0204a223ad0e44b2a330d4b189655da1-litigation-supervisor-family-defense-practice-bronx-center-for-family-representation-inc-new-york</t>
+  </si>
+  <si>
+    <t>Manager, Corporate Partnerships</t>
+  </si>
+  <si>
+    <t>Share Our Strength</t>
+  </si>
+  <si>
+    <t>USD 71000.00 - 79000.00/year</t>
+  </si>
+  <si>
+    <t>Poverty, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2c2eb5c87f5440d0a954e16e95b0cf6f-manager-corporate-partnerships-share-our-strength-washington</t>
+  </si>
+  <si>
+    <t>Marketing and Business Development Manager</t>
+  </si>
+  <si>
+    <t>All Out Africa</t>
+  </si>
+  <si>
+    <t>Ezulwini, Ezulwini, SZ</t>
+  </si>
+  <si>
+    <t>USD 16000.00 - 22000.00/year</t>
+  </si>
+  <si>
+    <t>Travel Hospitality, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/b6eb2a0cfcff49b68e4f7d5da46ed742-marketing-and-business-development-manager-all-out-africa-ezulwini</t>
+  </si>
+  <si>
+    <t>Middle School Inclusion Teacher (SY26-27)</t>
+  </si>
+  <si>
+    <t>Capital City Public Charter School</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 93000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a417226d3c9c41498c58c8f547529dfe-middle-school-inclusion-teacher-sy26-27-capital-city-public-charter-school-washington</t>
+  </si>
+  <si>
+    <t>NIH Clinical Center- Head of Bioethics Consultation Service</t>
+  </si>
+  <si>
+    <t>Department of Bioethics, Clinical Center, National Institutes of Health</t>
+  </si>
+  <si>
+    <t>Bethesda, Maryland</t>
+  </si>
+  <si>
+    <t>USD 169279.00 - 197200.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Research Social Science, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/e637df4b869647e4b83f43f355fe68d8-nih-clinical-center-head-of-bioethics-consultation-service-department-of-bioethics-clinical-center-national-institutes-of-health-bethesda</t>
+  </si>
+  <si>
+    <t>Oficial de Sostenibilidad - Puerto Plata RD</t>
+  </si>
+  <si>
+    <t>Fundación Genera</t>
+  </si>
+  <si>
+    <t>Puerto plata, Puerto Plata, DO</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a9df71534fec4b23879efe0cd1ae9b43-oficial-de-sostenibilidad-puerto-plata-rd-fundacion-genera-puerto-plata</t>
+  </si>
+  <si>
+    <t>Operations Director</t>
+  </si>
+  <si>
+    <t>WeShine: Welcoming, Empowering, Safe Habitation Initiative with Neighborhood Engagement</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 72800.00 - 76960.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bf6bcbe614044207b17a9399aca291bd-operations-director-weshine-welcoming-empowering-safe-habitation-initiative-with-neighborhood-engagement-portland</t>
+  </si>
+  <si>
+    <t>OST Director of ESY</t>
+  </si>
+  <si>
+    <t>Arts for Learning Maryland</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 84900.00 - 84900.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fc880cfa684c4eea985abc3646ba499e-ost-director-of-esy-arts-for-learning-maryland-baltimore</t>
+  </si>
+  <si>
+    <t>OST Director of SALA/Afterschool</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c2af837b586443518917707798b3ed2c-ost-director-of-salaafterschool-arts-for-learning-maryland-baltimore</t>
+  </si>
+  <si>
+    <t>Part-Time Research &amp; Program Associate</t>
+  </si>
+  <si>
+    <t>Raise the Rail, Inc.</t>
+  </si>
+  <si>
+    <t>brooklyn, New York</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Mental Health, Policy, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9df12a3f885d453e9cdc6754952aa61a-part-time-research-program-associate-raise-the-rail-inc-brooklyn</t>
+  </si>
+  <si>
+    <t>Partner Success Manager</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf13944cd24a4a1ea12eb2a54446e6ac-partner-success-manager-credential-engine-washington</t>
+  </si>
+  <si>
+    <t>Partnership and Resource Mobilisation Coordinator</t>
+  </si>
+  <si>
+    <t>International Detention Coalition</t>
+  </si>
+  <si>
+    <t>Remote (NL)</t>
+  </si>
+  <si>
+    <t>EUR 36000.00 - 42400.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a53b959f46247f7a603fd47cedc961b-partnership-and-resource-mobilisation-coordinator-international-detention-coalition-melbourne</t>
+  </si>
+  <si>
+    <t>Remote (GB)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f5ae809b07b4b28903957598ec9cc0e-partnership-and-resource-mobilisation-coordinator-international-detention-coalition-melbourne</t>
+  </si>
+  <si>
+    <t>Remote (DE)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5dfe7a08572c42699d0466d13e2a7590-partnership-and-resource-mobilisation-coordinator-international-detention-coalition-melbourne</t>
+  </si>
+  <si>
+    <t>Peer Specialist - Brooklyn Peer Advocacy</t>
+  </si>
+  <si>
+    <t>Baltic Street Wellness Solutions</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 41000.00 - 41000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Human Rights Civil Liberties, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8944d3090667426c837edb11a48bd481-peer-specialist-brooklyn-peer-advocacy-baltic-street-wellness-solutions-kings-county</t>
+  </si>
+  <si>
+    <t>Planned Giving Coordinator</t>
+  </si>
+  <si>
+    <t>Environmental Defense Fund</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/04292126b07b436b966a89af23689343-planned-giving-coordinator-environmental-defense-fund-new-york</t>
+  </si>
+  <si>
+    <t>plus más media, Digital Media Associate, Studio Operations Associate (Full Time, Remote)</t>
+  </si>
+  <si>
+    <t>Accelerate Change</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5018fbf573ba4dbfa76d59d1e99eda7e-plus-mas-media-digital-media-associate-studio-operations-associate-full-time-remote-accelerate-change-washington</t>
+  </si>
+  <si>
+    <t>Political Associate</t>
+  </si>
+  <si>
+    <t>Reproductive Freedom for All</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Policy, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d16a82bcc984a8aab7b6d544cf56fcb-political-associate-reproductive-freedom-for-all-washington</t>
+  </si>
+  <si>
+    <t>Program Data Specialist</t>
+  </si>
+  <si>
+    <t>Masa</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7ecf46d1fd5c4d47a0d0fc2c01bfebd2-program-data-specialist-masa-bronx</t>
+  </si>
+  <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>Global Greengrants Fund</t>
+  </si>
+  <si>
+    <t>USD 102800.00 - 102800.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a8a8275c0e3479693034cc15a8c06f5-program-manager-global-greengrants-fund-boulder</t>
+  </si>
+  <si>
+    <t>Foundation for the Mid South, Inc. (60507)</t>
+  </si>
+  <si>
+    <t>Jackson, Mississippi</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b6917af37b5849b4bb2d2b2aeee10117-program-manager-foundation-for-the-mid-south-inc-60507-jackson</t>
+  </si>
+  <si>
+    <t>Regional Manager - Los Angeles</t>
+  </si>
+  <si>
+    <t>Back 2 Work</t>
+  </si>
+  <si>
+    <t>USD 95862.00 - 122343.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Veterans</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/f42edfbfa0a0437f87213fa5b09b2ce8-regional-manager-los-angeles-back-2-work-los-angeles</t>
+  </si>
+  <si>
+    <t>Senior Advisor, Project Management</t>
+  </si>
+  <si>
+    <t>BME Strategies</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/83aab0e822cb43cf954c5948e12c9ecc-senior-advisor-project-management-bme-strategies-north-andover</t>
+  </si>
+  <si>
+    <t>Senior Director of Visitor Services and Business Development</t>
+  </si>
+  <si>
+    <t>Wave Hill (Bronx, New York)</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/66c78e8ac80b4689b50951284a07ab59-senior-director-of-visitor-services-and-business-development-wave-hill-bronx-new-york-bronx</t>
+  </si>
+  <si>
+    <t>Senior Director, Leadership Giving</t>
+  </si>
+  <si>
+    <t>National Audubon Society</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 186000.00 - 208000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5426efbb22dd47f4aff02ed46e6ce202-senior-director-leadership-giving-national-audubon-society-oakland</t>
+  </si>
+  <si>
+    <t>Senior Ethics &amp; Professional Review Associate</t>
+  </si>
+  <si>
+    <t>National Association of Social Workers</t>
+  </si>
+  <si>
+    <t>USD 93000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/027b884033c74d21b5ffc7b3d639c573-senior-ethics-professional-review-associate-national-association-of-social-workers-washington</t>
+  </si>
+  <si>
+    <t>Senior Peer Specialist - Community Links</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3c04a0af4f4442c0af9e2c198c95e88a-senior-peer-specialist-community-links-baltic-street-wellness-solutions-kings-county</t>
+  </si>
+  <si>
+    <t>Senior Research Assistant, The Hamilton Project (Job ID: 2026-3892)</t>
+  </si>
+  <si>
+    <t>1. Resident Employee (Hybrid)</t>
+  </si>
+  <si>
+    <t>USD 50300.00 - 75400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/2538e1fa7501497697e3dc127da27376-senior-research-assistant-the-hamilton-project-job-id-2026-3892-1-resident-employee-hybrid-washington</t>
+  </si>
+  <si>
+    <t>Senior Social Worker - Mobile Crisis Response Team (MCRT)</t>
+  </si>
+  <si>
+    <t>People USA</t>
+  </si>
+  <si>
+    <t>New Rochelle, New York</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2bb58807e2d947c6a854f7be8cb7d5e3-senior-social-worker-mobile-crisis-response-team-mcrt-people-usa-new-rochelle</t>
+  </si>
+  <si>
+    <t>Senior Staff Attorney, Clean Energy &amp; Green Finance</t>
+  </si>
+  <si>
+    <t>Lawyers for Good Government</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Human Rights Civil Liberties, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c24e802e507a4fad89cb5ba631607a93-senior-staff-attorney-clean-energy-green-finance-lawyers-for-good-government-washington</t>
+  </si>
+  <si>
+    <t>Site Manager, GreenLight Fund Detroit</t>
+  </si>
+  <si>
+    <t>GreenLight Fund</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/136144e1760c4538a01b962e7ae3671f-site-manager-greenlight-fund-detroit-greenlight-fund-detroit</t>
+  </si>
+  <si>
+    <t>Social Work Supervisor (forensic), Bronx</t>
+  </si>
+  <si>
+    <t>USD 107100.00 - 120200.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b606402951d4356b6846dc90ee6161c-social-work-supervisor-forensic-bronx-center-for-family-representation-inc-new-york</t>
+  </si>
+  <si>
+    <t>Sr. Social Worker</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c6f84f7811bc428e8909018be110f7b4-sr-social-worker-central-union-mission-washington</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>Mass Audubon Metro West</t>
+  </si>
+  <si>
+    <t>Lincoln, Massachusetts</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/26b0e967545941dbbee0e3d153574c74-staff-accountant-mass-audubon-metro-west-lincoln</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union of Arkansas</t>
+  </si>
+  <si>
+    <t>Little Rock, Arkansas</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6ded5880f0f64d94a5adfbbabff237ef-staff-attorney-american-civil-liberties-union-of-arkansas-little-rock</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Family Defense Practice, Queens</t>
+  </si>
+  <si>
+    <t>USD 95700.00 - 126300.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d0da5804d4945b99c77e32c155bc9a5-staff-attorney-family-defense-practice-queens-center-for-family-representation-inc-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Hogar [Home] Program</t>
+  </si>
+  <si>
+    <t>National Center for LGBTQ Rights</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 95143.00 - 153557.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Lgbtq, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/48b2c917e06b4a8e81fd586e09cce70c-staff-attorney-hogar-home-program-national-center-for-lgbtq-rights-san-francisco</t>
+  </si>
+  <si>
+    <t>Supported Education Counselor - Full Time</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d04b2907b8fc46fdb8d4ad53ec22d425-supported-education-counselor-full-time-baltic-street-wellness-solutions-kings-county</t>
+  </si>
+  <si>
+    <t>Visiting Counselors- ATP</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f08dbf71e6d24c4cb67012d86068f28f-visiting-counselors-atp-geel-community-services-inc-the-bronx</t>
+  </si>
+  <si>
+    <t>Weekend Program Assistant</t>
+  </si>
+  <si>
+    <t>SELAH NEIGHBORHOOD HOMELESS COALITION</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cbf6cc3186c5478d811ea6c34ca43183-weekend-program-assistant-selah-neighborhood-homeless-coalition-los-angeles</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +2037,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +2063,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2445,898 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" t="s">
+        <v>58</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" t="s">
+        <v>92</v>
+      </c>
+      <c r="F18" t="s">
+        <v>93</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" t="s">
+        <v>103</v>
+      </c>
+      <c r="F20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" t="s">
+        <v>109</v>
+      </c>
+      <c r="F21" t="s">
+        <v>110</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" t="s">
+        <v>116</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" t="s">
+        <v>124</v>
+      </c>
+      <c r="F24" t="s">
+        <v>58</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" t="s">
+        <v>133</v>
+      </c>
+      <c r="D26" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F26" t="s">
+        <v>136</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" t="s">
+        <v>139</v>
+      </c>
+      <c r="C27" t="s">
+        <v>140</v>
+      </c>
+      <c r="D27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F27" t="s">
+        <v>142</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" t="s">
+        <v>146</v>
+      </c>
+      <c r="D28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" t="s">
+        <v>147</v>
+      </c>
+      <c r="F28" t="s">
+        <v>148</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" t="s">
+        <v>153</v>
+      </c>
+      <c r="F29" t="s">
+        <v>99</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>155</v>
+      </c>
+      <c r="B30" t="s">
+        <v>156</v>
+      </c>
+      <c r="C30" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" t="s">
+        <v>158</v>
+      </c>
+      <c r="F30" t="s">
+        <v>110</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" t="s">
+        <v>161</v>
+      </c>
+      <c r="C31" t="s">
+        <v>162</v>
+      </c>
+      <c r="D31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" t="s">
+        <v>163</v>
+      </c>
+      <c r="F31" t="s">
+        <v>164</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>166</v>
+      </c>
+      <c r="B32" t="s">
+        <v>167</v>
+      </c>
+      <c r="C32" t="s">
+        <v>168</v>
+      </c>
+      <c r="D32" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" t="s">
+        <v>169</v>
+      </c>
+      <c r="F32" t="s">
+        <v>170</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>172</v>
+      </c>
+      <c r="B33" t="s">
+        <v>173</v>
+      </c>
+      <c r="C33" t="s">
+        <v>174</v>
+      </c>
+      <c r="D33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" t="s">
+        <v>175</v>
+      </c>
+      <c r="F33" t="s">
+        <v>176</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B34" t="s">
+        <v>179</v>
+      </c>
+      <c r="C34" t="s">
+        <v>180</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>181</v>
+      </c>
+      <c r="F34" t="s">
+        <v>182</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>184</v>
+      </c>
+      <c r="B35" t="s">
+        <v>185</v>
+      </c>
+      <c r="C35" t="s">
+        <v>186</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" t="s">
+        <v>187</v>
+      </c>
+      <c r="F35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>189</v>
+      </c>
+      <c r="B36" t="s">
+        <v>185</v>
+      </c>
+      <c r="C36" t="s">
+        <v>190</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" t="s">
+        <v>191</v>
+      </c>
+      <c r="F36" t="s">
+        <v>192</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>194</v>
+      </c>
+      <c r="B37" t="s">
+        <v>195</v>
+      </c>
+      <c r="C37" t="s">
+        <v>196</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>197</v>
+      </c>
+      <c r="F37" t="s">
+        <v>198</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>200</v>
+      </c>
+      <c r="B38" t="s">
+        <v>201</v>
+      </c>
+      <c r="C38" t="s">
+        <v>202</v>
+      </c>
+      <c r="D38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" t="s">
+        <v>203</v>
+      </c>
+      <c r="F38" t="s">
+        <v>170</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -466,7 +3344,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -505,8 +3383,82 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2" t="s">
+        <v>210</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F3" t="s">
+        <v>210</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" t="s">
+        <v>210</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3466,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3505,2266 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F3" t="s">
+        <v>227</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D4" t="s">
+        <v>219</v>
+      </c>
+      <c r="E4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F4" t="s">
+        <v>232</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D5" t="s">
+        <v>219</v>
+      </c>
+      <c r="E5" t="s">
+        <v>237</v>
+      </c>
+      <c r="F5" t="s">
+        <v>238</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E6" t="s">
+        <v>243</v>
+      </c>
+      <c r="F6" t="s">
+        <v>244</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D7" t="s">
+        <v>249</v>
+      </c>
+      <c r="E7" t="s">
+        <v>250</v>
+      </c>
+      <c r="F7" t="s">
+        <v>251</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>255</v>
+      </c>
+      <c r="D8" t="s">
+        <v>219</v>
+      </c>
+      <c r="E8" t="s">
+        <v>256</v>
+      </c>
+      <c r="F8" t="s">
+        <v>226</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>258</v>
+      </c>
+      <c r="B9" t="s">
+        <v>259</v>
+      </c>
+      <c r="C9" t="s">
+        <v>260</v>
+      </c>
+      <c r="D9" t="s">
+        <v>219</v>
+      </c>
+      <c r="E9" t="s">
+        <v>261</v>
+      </c>
+      <c r="F9" t="s">
+        <v>262</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>264</v>
+      </c>
+      <c r="B10" t="s">
+        <v>265</v>
+      </c>
+      <c r="C10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D10" t="s">
+        <v>219</v>
+      </c>
+      <c r="E10" t="s">
+        <v>267</v>
+      </c>
+      <c r="F10" t="s">
+        <v>268</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>270</v>
+      </c>
+      <c r="B11" t="s">
+        <v>271</v>
+      </c>
+      <c r="C11" t="s">
+        <v>272</v>
+      </c>
+      <c r="D11" t="s">
+        <v>273</v>
+      </c>
+      <c r="E11" t="s">
+        <v>226</v>
+      </c>
+      <c r="F11" t="s">
+        <v>274</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>276</v>
+      </c>
+      <c r="B12" t="s">
+        <v>277</v>
+      </c>
+      <c r="C12" t="s">
+        <v>218</v>
+      </c>
+      <c r="D12" t="s">
+        <v>273</v>
+      </c>
+      <c r="E12" t="s">
+        <v>278</v>
+      </c>
+      <c r="F12" t="s">
+        <v>279</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B13" t="s">
+        <v>282</v>
+      </c>
+      <c r="C13" t="s">
+        <v>283</v>
+      </c>
+      <c r="D13" t="s">
+        <v>219</v>
+      </c>
+      <c r="E13" t="s">
+        <v>284</v>
+      </c>
+      <c r="F13" t="s">
+        <v>226</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B14" t="s">
+        <v>282</v>
+      </c>
+      <c r="C14" t="s">
+        <v>283</v>
+      </c>
+      <c r="D14" t="s">
+        <v>219</v>
+      </c>
+      <c r="E14" t="s">
+        <v>287</v>
+      </c>
+      <c r="F14" t="s">
+        <v>288</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>290</v>
+      </c>
+      <c r="B15" t="s">
+        <v>291</v>
+      </c>
+      <c r="C15" t="s">
+        <v>292</v>
+      </c>
+      <c r="D15" t="s">
+        <v>219</v>
+      </c>
+      <c r="E15" t="s">
+        <v>293</v>
+      </c>
+      <c r="F15" t="s">
+        <v>226</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>295</v>
+      </c>
+      <c r="B16" t="s">
+        <v>296</v>
+      </c>
+      <c r="C16" t="s">
+        <v>297</v>
+      </c>
+      <c r="D16" t="s">
+        <v>219</v>
+      </c>
+      <c r="E16" t="s">
+        <v>298</v>
+      </c>
+      <c r="F16" t="s">
+        <v>299</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>301</v>
+      </c>
+      <c r="B17" t="s">
+        <v>302</v>
+      </c>
+      <c r="C17" t="s">
+        <v>303</v>
+      </c>
+      <c r="D17" t="s">
+        <v>219</v>
+      </c>
+      <c r="E17" t="s">
+        <v>304</v>
+      </c>
+      <c r="F17" t="s">
+        <v>305</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>307</v>
+      </c>
+      <c r="B18" t="s">
+        <v>308</v>
+      </c>
+      <c r="C18" t="s">
+        <v>218</v>
+      </c>
+      <c r="D18" t="s">
+        <v>219</v>
+      </c>
+      <c r="E18" t="s">
+        <v>309</v>
+      </c>
+      <c r="F18" t="s">
+        <v>310</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>312</v>
+      </c>
+      <c r="B19" t="s">
+        <v>313</v>
+      </c>
+      <c r="C19" t="s">
+        <v>314</v>
+      </c>
+      <c r="D19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E19" t="s">
+        <v>315</v>
+      </c>
+      <c r="F19" t="s">
+        <v>316</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>318</v>
+      </c>
+      <c r="B20" t="s">
+        <v>254</v>
+      </c>
+      <c r="C20" t="s">
+        <v>260</v>
+      </c>
+      <c r="D20" t="s">
+        <v>219</v>
+      </c>
+      <c r="E20" t="s">
+        <v>319</v>
+      </c>
+      <c r="F20" t="s">
+        <v>226</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>321</v>
+      </c>
+      <c r="B21" t="s">
+        <v>322</v>
+      </c>
+      <c r="C21" t="s">
+        <v>260</v>
+      </c>
+      <c r="D21" t="s">
+        <v>219</v>
+      </c>
+      <c r="E21" t="s">
+        <v>323</v>
+      </c>
+      <c r="F21" t="s">
+        <v>324</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" t="s">
+        <v>326</v>
+      </c>
+      <c r="C22" t="s">
+        <v>327</v>
+      </c>
+      <c r="D22" t="s">
+        <v>219</v>
+      </c>
+      <c r="E22" t="s">
+        <v>328</v>
+      </c>
+      <c r="F22" t="s">
+        <v>226</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>330</v>
+      </c>
+      <c r="B23" t="s">
+        <v>331</v>
+      </c>
+      <c r="C23" t="s">
+        <v>303</v>
+      </c>
+      <c r="D23" t="s">
+        <v>219</v>
+      </c>
+      <c r="E23" t="s">
+        <v>332</v>
+      </c>
+      <c r="F23" t="s">
+        <v>333</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>335</v>
+      </c>
+      <c r="B24" t="s">
+        <v>336</v>
+      </c>
+      <c r="C24" t="s">
+        <v>337</v>
+      </c>
+      <c r="D24" t="s">
+        <v>219</v>
+      </c>
+      <c r="E24" t="s">
+        <v>267</v>
+      </c>
+      <c r="F24" t="s">
+        <v>338</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>340</v>
+      </c>
+      <c r="B25" t="s">
+        <v>341</v>
+      </c>
+      <c r="C25" t="s">
+        <v>342</v>
+      </c>
+      <c r="D25" t="s">
+        <v>219</v>
+      </c>
+      <c r="E25" t="s">
+        <v>343</v>
+      </c>
+      <c r="F25" t="s">
+        <v>344</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>346</v>
+      </c>
+      <c r="B26" t="s">
+        <v>347</v>
+      </c>
+      <c r="C26" t="s">
+        <v>348</v>
+      </c>
+      <c r="D26" t="s">
+        <v>219</v>
+      </c>
+      <c r="E26" t="s">
+        <v>349</v>
+      </c>
+      <c r="F26" t="s">
+        <v>350</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>352</v>
+      </c>
+      <c r="B27" t="s">
+        <v>353</v>
+      </c>
+      <c r="C27" t="s">
+        <v>354</v>
+      </c>
+      <c r="D27" t="s">
+        <v>219</v>
+      </c>
+      <c r="E27" t="s">
+        <v>226</v>
+      </c>
+      <c r="F27" t="s">
+        <v>355</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>357</v>
+      </c>
+      <c r="B28" t="s">
+        <v>358</v>
+      </c>
+      <c r="C28" t="s">
+        <v>260</v>
+      </c>
+      <c r="D28" t="s">
+        <v>219</v>
+      </c>
+      <c r="E28" t="s">
+        <v>359</v>
+      </c>
+      <c r="F28" t="s">
+        <v>360</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>362</v>
+      </c>
+      <c r="B29" t="s">
+        <v>363</v>
+      </c>
+      <c r="C29" t="s">
+        <v>260</v>
+      </c>
+      <c r="D29" t="s">
+        <v>219</v>
+      </c>
+      <c r="E29" t="s">
+        <v>364</v>
+      </c>
+      <c r="F29" t="s">
+        <v>365</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>367</v>
+      </c>
+      <c r="B30" t="s">
+        <v>368</v>
+      </c>
+      <c r="C30" t="s">
+        <v>218</v>
+      </c>
+      <c r="D30" t="s">
+        <v>219</v>
+      </c>
+      <c r="E30" t="s">
+        <v>369</v>
+      </c>
+      <c r="F30" t="s">
+        <v>370</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>372</v>
+      </c>
+      <c r="B31" t="s">
+        <v>373</v>
+      </c>
+      <c r="C31" t="s">
+        <v>374</v>
+      </c>
+      <c r="D31" t="s">
+        <v>219</v>
+      </c>
+      <c r="E31" t="s">
+        <v>375</v>
+      </c>
+      <c r="F31" t="s">
+        <v>376</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>378</v>
+      </c>
+      <c r="B32" t="s">
+        <v>379</v>
+      </c>
+      <c r="C32" t="s">
+        <v>380</v>
+      </c>
+      <c r="D32" t="s">
+        <v>219</v>
+      </c>
+      <c r="E32" t="s">
+        <v>381</v>
+      </c>
+      <c r="F32" t="s">
+        <v>382</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>384</v>
+      </c>
+      <c r="B33" t="s">
+        <v>353</v>
+      </c>
+      <c r="C33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D33" t="s">
+        <v>219</v>
+      </c>
+      <c r="E33" t="s">
+        <v>226</v>
+      </c>
+      <c r="F33" t="s">
+        <v>355</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>386</v>
+      </c>
+      <c r="B34" t="s">
+        <v>387</v>
+      </c>
+      <c r="C34" t="s">
+        <v>260</v>
+      </c>
+      <c r="D34" t="s">
+        <v>219</v>
+      </c>
+      <c r="E34" t="s">
+        <v>388</v>
+      </c>
+      <c r="F34" t="s">
+        <v>238</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>390</v>
+      </c>
+      <c r="B35" t="s">
+        <v>391</v>
+      </c>
+      <c r="C35" t="s">
+        <v>392</v>
+      </c>
+      <c r="D35" t="s">
+        <v>219</v>
+      </c>
+      <c r="E35" t="s">
+        <v>393</v>
+      </c>
+      <c r="F35" t="s">
+        <v>394</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>396</v>
+      </c>
+      <c r="B36" t="s">
+        <v>397</v>
+      </c>
+      <c r="C36" t="s">
+        <v>398</v>
+      </c>
+      <c r="D36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E36" t="s">
+        <v>226</v>
+      </c>
+      <c r="F36" t="s">
+        <v>399</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>401</v>
+      </c>
+      <c r="B37" t="s">
+        <v>402</v>
+      </c>
+      <c r="C37" t="s">
+        <v>403</v>
+      </c>
+      <c r="D37" t="s">
+        <v>219</v>
+      </c>
+      <c r="E37" t="s">
+        <v>328</v>
+      </c>
+      <c r="F37" t="s">
+        <v>376</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>405</v>
+      </c>
+      <c r="B38" t="s">
+        <v>308</v>
+      </c>
+      <c r="C38" t="s">
+        <v>218</v>
+      </c>
+      <c r="D38" t="s">
+        <v>249</v>
+      </c>
+      <c r="E38" t="s">
+        <v>406</v>
+      </c>
+      <c r="F38" t="s">
+        <v>310</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>408</v>
+      </c>
+      <c r="B39" t="s">
+        <v>409</v>
+      </c>
+      <c r="C39" t="s">
+        <v>242</v>
+      </c>
+      <c r="D39" t="s">
+        <v>219</v>
+      </c>
+      <c r="E39" t="s">
+        <v>410</v>
+      </c>
+      <c r="F39" t="s">
+        <v>226</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" t="s">
+        <v>412</v>
+      </c>
+      <c r="C40" t="s">
+        <v>413</v>
+      </c>
+      <c r="D40" t="s">
+        <v>219</v>
+      </c>
+      <c r="E40" t="s">
+        <v>414</v>
+      </c>
+      <c r="F40" t="s">
+        <v>415</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" t="s">
+        <v>417</v>
+      </c>
+      <c r="C41" t="s">
+        <v>418</v>
+      </c>
+      <c r="D41" t="s">
+        <v>249</v>
+      </c>
+      <c r="E41" t="s">
+        <v>419</v>
+      </c>
+      <c r="F41" t="s">
+        <v>420</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>422</v>
+      </c>
+      <c r="B42" t="s">
+        <v>423</v>
+      </c>
+      <c r="C42" t="s">
+        <v>327</v>
+      </c>
+      <c r="D42" t="s">
+        <v>219</v>
+      </c>
+      <c r="E42" t="s">
+        <v>424</v>
+      </c>
+      <c r="F42" t="s">
+        <v>425</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>427</v>
+      </c>
+      <c r="B43" t="s">
+        <v>428</v>
+      </c>
+      <c r="C43" t="s">
+        <v>429</v>
+      </c>
+      <c r="D43" t="s">
+        <v>219</v>
+      </c>
+      <c r="E43" t="s">
+        <v>430</v>
+      </c>
+      <c r="F43" t="s">
+        <v>431</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>433</v>
+      </c>
+      <c r="B44" t="s">
+        <v>391</v>
+      </c>
+      <c r="C44" t="s">
+        <v>392</v>
+      </c>
+      <c r="D44" t="s">
+        <v>219</v>
+      </c>
+      <c r="E44" t="s">
+        <v>434</v>
+      </c>
+      <c r="F44" t="s">
+        <v>435</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>437</v>
+      </c>
+      <c r="B45" t="s">
+        <v>438</v>
+      </c>
+      <c r="C45" t="s">
+        <v>439</v>
+      </c>
+      <c r="D45" t="s">
+        <v>219</v>
+      </c>
+      <c r="E45" t="s">
+        <v>440</v>
+      </c>
+      <c r="F45" t="s">
+        <v>226</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>442</v>
+      </c>
+      <c r="B46" t="s">
+        <v>443</v>
+      </c>
+      <c r="C46" t="s">
+        <v>444</v>
+      </c>
+      <c r="D46" t="s">
+        <v>219</v>
+      </c>
+      <c r="E46" t="s">
+        <v>445</v>
+      </c>
+      <c r="F46" t="s">
+        <v>446</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>448</v>
+      </c>
+      <c r="B47" t="s">
+        <v>449</v>
+      </c>
+      <c r="C47" t="s">
+        <v>450</v>
+      </c>
+      <c r="D47" t="s">
+        <v>219</v>
+      </c>
+      <c r="E47" t="s">
+        <v>451</v>
+      </c>
+      <c r="F47" t="s">
+        <v>452</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>454</v>
+      </c>
+      <c r="B48" t="s">
+        <v>455</v>
+      </c>
+      <c r="C48" t="s">
+        <v>218</v>
+      </c>
+      <c r="D48" t="s">
+        <v>249</v>
+      </c>
+      <c r="E48" t="s">
+        <v>456</v>
+      </c>
+      <c r="F48" t="s">
+        <v>360</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>458</v>
+      </c>
+      <c r="B49" t="s">
+        <v>459</v>
+      </c>
+      <c r="C49" t="s">
+        <v>303</v>
+      </c>
+      <c r="D49" t="s">
+        <v>219</v>
+      </c>
+      <c r="E49" t="s">
+        <v>460</v>
+      </c>
+      <c r="F49" t="s">
+        <v>461</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>463</v>
+      </c>
+      <c r="B50" t="s">
+        <v>423</v>
+      </c>
+      <c r="C50" t="s">
+        <v>327</v>
+      </c>
+      <c r="D50" t="s">
+        <v>219</v>
+      </c>
+      <c r="E50" t="s">
+        <v>464</v>
+      </c>
+      <c r="F50" t="s">
+        <v>425</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>466</v>
+      </c>
+      <c r="B51" t="s">
+        <v>467</v>
+      </c>
+      <c r="C51" t="s">
+        <v>468</v>
+      </c>
+      <c r="D51" t="s">
+        <v>219</v>
+      </c>
+      <c r="E51" t="s">
+        <v>469</v>
+      </c>
+      <c r="F51" t="s">
+        <v>470</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>472</v>
+      </c>
+      <c r="B52" t="s">
+        <v>473</v>
+      </c>
+      <c r="C52" t="s">
+        <v>474</v>
+      </c>
+      <c r="D52" t="s">
+        <v>219</v>
+      </c>
+      <c r="E52" t="s">
+        <v>226</v>
+      </c>
+      <c r="F52" t="s">
+        <v>475</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>477</v>
+      </c>
+      <c r="B53" t="s">
+        <v>438</v>
+      </c>
+      <c r="C53" t="s">
+        <v>478</v>
+      </c>
+      <c r="D53" t="s">
+        <v>219</v>
+      </c>
+      <c r="E53" t="s">
+        <v>388</v>
+      </c>
+      <c r="F53" t="s">
+        <v>226</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>480</v>
+      </c>
+      <c r="B54" t="s">
+        <v>481</v>
+      </c>
+      <c r="C54" t="s">
+        <v>482</v>
+      </c>
+      <c r="D54" t="s">
+        <v>219</v>
+      </c>
+      <c r="E54" t="s">
+        <v>483</v>
+      </c>
+      <c r="F54" t="s">
+        <v>484</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>486</v>
+      </c>
+      <c r="B55" t="s">
+        <v>481</v>
+      </c>
+      <c r="C55" t="s">
+        <v>487</v>
+      </c>
+      <c r="D55" t="s">
+        <v>219</v>
+      </c>
+      <c r="E55" t="s">
+        <v>483</v>
+      </c>
+      <c r="F55" t="s">
+        <v>484</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>489</v>
+      </c>
+      <c r="B56" t="s">
+        <v>490</v>
+      </c>
+      <c r="C56" t="s">
+        <v>260</v>
+      </c>
+      <c r="D56" t="s">
+        <v>219</v>
+      </c>
+      <c r="E56" t="s">
+        <v>491</v>
+      </c>
+      <c r="F56" t="s">
+        <v>492</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>494</v>
+      </c>
+      <c r="B57" t="s">
+        <v>495</v>
+      </c>
+      <c r="C57" t="s">
+        <v>327</v>
+      </c>
+      <c r="D57" t="s">
+        <v>219</v>
+      </c>
+      <c r="E57" t="s">
+        <v>496</v>
+      </c>
+      <c r="F57" t="s">
+        <v>497</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>499</v>
+      </c>
+      <c r="B58" t="s">
+        <v>500</v>
+      </c>
+      <c r="C58" t="s">
+        <v>501</v>
+      </c>
+      <c r="D58" t="s">
+        <v>219</v>
+      </c>
+      <c r="E58" t="s">
+        <v>502</v>
+      </c>
+      <c r="F58" t="s">
+        <v>503</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>505</v>
+      </c>
+      <c r="B59" t="s">
+        <v>506</v>
+      </c>
+      <c r="C59" t="s">
+        <v>327</v>
+      </c>
+      <c r="D59" t="s">
+        <v>219</v>
+      </c>
+      <c r="E59" t="s">
+        <v>507</v>
+      </c>
+      <c r="F59" t="s">
+        <v>232</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>509</v>
+      </c>
+      <c r="B60" t="s">
+        <v>510</v>
+      </c>
+      <c r="C60" t="s">
+        <v>511</v>
+      </c>
+      <c r="D60" t="s">
+        <v>219</v>
+      </c>
+      <c r="E60" t="s">
+        <v>512</v>
+      </c>
+      <c r="F60" t="s">
+        <v>513</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>515</v>
+      </c>
+      <c r="B61" t="s">
+        <v>516</v>
+      </c>
+      <c r="C61" t="s">
+        <v>517</v>
+      </c>
+      <c r="D61" t="s">
+        <v>219</v>
+      </c>
+      <c r="E61" t="s">
+        <v>226</v>
+      </c>
+      <c r="F61" t="s">
+        <v>518</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>520</v>
+      </c>
+      <c r="B62" t="s">
+        <v>521</v>
+      </c>
+      <c r="C62" t="s">
+        <v>522</v>
+      </c>
+      <c r="D62" t="s">
+        <v>219</v>
+      </c>
+      <c r="E62" t="s">
+        <v>523</v>
+      </c>
+      <c r="F62" t="s">
+        <v>262</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>525</v>
+      </c>
+      <c r="B63" t="s">
+        <v>526</v>
+      </c>
+      <c r="C63" t="s">
+        <v>527</v>
+      </c>
+      <c r="D63" t="s">
+        <v>219</v>
+      </c>
+      <c r="E63" t="s">
+        <v>528</v>
+      </c>
+      <c r="F63" t="s">
+        <v>305</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>530</v>
+      </c>
+      <c r="B64" t="s">
+        <v>526</v>
+      </c>
+      <c r="C64" t="s">
+        <v>527</v>
+      </c>
+      <c r="D64" t="s">
+        <v>219</v>
+      </c>
+      <c r="E64" t="s">
+        <v>528</v>
+      </c>
+      <c r="F64" t="s">
+        <v>305</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>532</v>
+      </c>
+      <c r="B65" t="s">
+        <v>533</v>
+      </c>
+      <c r="C65" t="s">
+        <v>534</v>
+      </c>
+      <c r="D65" t="s">
+        <v>249</v>
+      </c>
+      <c r="E65" t="s">
+        <v>535</v>
+      </c>
+      <c r="F65" t="s">
+        <v>536</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>538</v>
+      </c>
+      <c r="B66" t="s">
+        <v>368</v>
+      </c>
+      <c r="C66" t="s">
+        <v>218</v>
+      </c>
+      <c r="D66" t="s">
+        <v>219</v>
+      </c>
+      <c r="E66" t="s">
+        <v>539</v>
+      </c>
+      <c r="F66" t="s">
+        <v>370</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>541</v>
+      </c>
+      <c r="B67" t="s">
+        <v>542</v>
+      </c>
+      <c r="C67" t="s">
+        <v>543</v>
+      </c>
+      <c r="D67" t="s">
+        <v>219</v>
+      </c>
+      <c r="E67" t="s">
+        <v>544</v>
+      </c>
+      <c r="F67" t="s">
+        <v>545</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>541</v>
+      </c>
+      <c r="B68" t="s">
+        <v>542</v>
+      </c>
+      <c r="C68" t="s">
+        <v>547</v>
+      </c>
+      <c r="D68" t="s">
+        <v>219</v>
+      </c>
+      <c r="E68" t="s">
+        <v>544</v>
+      </c>
+      <c r="F68" t="s">
+        <v>545</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>541</v>
+      </c>
+      <c r="B69" t="s">
+        <v>542</v>
+      </c>
+      <c r="C69" t="s">
+        <v>549</v>
+      </c>
+      <c r="D69" t="s">
+        <v>219</v>
+      </c>
+      <c r="E69" t="s">
+        <v>544</v>
+      </c>
+      <c r="F69" t="s">
+        <v>545</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>551</v>
+      </c>
+      <c r="B70" t="s">
+        <v>552</v>
+      </c>
+      <c r="C70" t="s">
+        <v>553</v>
+      </c>
+      <c r="D70" t="s">
+        <v>219</v>
+      </c>
+      <c r="E70" t="s">
+        <v>554</v>
+      </c>
+      <c r="F70" t="s">
+        <v>555</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>557</v>
+      </c>
+      <c r="B71" t="s">
+        <v>558</v>
+      </c>
+      <c r="C71" t="s">
+        <v>260</v>
+      </c>
+      <c r="D71" t="s">
+        <v>559</v>
+      </c>
+      <c r="E71" t="s">
+        <v>560</v>
+      </c>
+      <c r="F71" t="s">
+        <v>561</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>563</v>
+      </c>
+      <c r="B72" t="s">
+        <v>564</v>
+      </c>
+      <c r="C72" t="s">
+        <v>218</v>
+      </c>
+      <c r="D72" t="s">
+        <v>219</v>
+      </c>
+      <c r="E72" t="s">
+        <v>565</v>
+      </c>
+      <c r="F72" t="s">
+        <v>566</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>568</v>
+      </c>
+      <c r="B73" t="s">
+        <v>569</v>
+      </c>
+      <c r="C73" t="s">
+        <v>327</v>
+      </c>
+      <c r="D73" t="s">
+        <v>219</v>
+      </c>
+      <c r="E73" t="s">
+        <v>570</v>
+      </c>
+      <c r="F73" t="s">
+        <v>571</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>573</v>
+      </c>
+      <c r="B74" t="s">
+        <v>574</v>
+      </c>
+      <c r="C74" t="s">
+        <v>575</v>
+      </c>
+      <c r="D74" t="s">
+        <v>559</v>
+      </c>
+      <c r="E74" t="s">
+        <v>406</v>
+      </c>
+      <c r="F74" t="s">
+        <v>576</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>578</v>
+      </c>
+      <c r="B75" t="s">
+        <v>579</v>
+      </c>
+      <c r="C75" t="s">
+        <v>218</v>
+      </c>
+      <c r="D75" t="s">
+        <v>219</v>
+      </c>
+      <c r="E75" t="s">
+        <v>580</v>
+      </c>
+      <c r="F75" t="s">
+        <v>581</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>578</v>
+      </c>
+      <c r="B76" t="s">
+        <v>583</v>
+      </c>
+      <c r="C76" t="s">
+        <v>584</v>
+      </c>
+      <c r="D76" t="s">
+        <v>219</v>
+      </c>
+      <c r="E76" t="s">
+        <v>585</v>
+      </c>
+      <c r="F76" t="s">
+        <v>586</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>588</v>
+      </c>
+      <c r="B77" t="s">
+        <v>589</v>
+      </c>
+      <c r="C77" t="s">
+        <v>248</v>
+      </c>
+      <c r="D77" t="s">
+        <v>219</v>
+      </c>
+      <c r="E77" t="s">
+        <v>590</v>
+      </c>
+      <c r="F77" t="s">
+        <v>591</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>593</v>
+      </c>
+      <c r="B78" t="s">
+        <v>594</v>
+      </c>
+      <c r="C78" t="s">
+        <v>218</v>
+      </c>
+      <c r="D78" t="s">
+        <v>219</v>
+      </c>
+      <c r="E78" t="s">
+        <v>226</v>
+      </c>
+      <c r="F78" t="s">
+        <v>595</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>597</v>
+      </c>
+      <c r="B79" t="s">
+        <v>598</v>
+      </c>
+      <c r="C79" t="s">
+        <v>575</v>
+      </c>
+      <c r="D79" t="s">
+        <v>219</v>
+      </c>
+      <c r="E79" t="s">
+        <v>599</v>
+      </c>
+      <c r="F79" t="s">
+        <v>226</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>601</v>
+      </c>
+      <c r="B80" t="s">
+        <v>602</v>
+      </c>
+      <c r="C80" t="s">
+        <v>603</v>
+      </c>
+      <c r="D80" t="s">
+        <v>219</v>
+      </c>
+      <c r="E80" t="s">
+        <v>604</v>
+      </c>
+      <c r="F80" t="s">
+        <v>605</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>607</v>
+      </c>
+      <c r="B81" t="s">
+        <v>608</v>
+      </c>
+      <c r="C81" t="s">
+        <v>327</v>
+      </c>
+      <c r="D81" t="s">
+        <v>219</v>
+      </c>
+      <c r="E81" t="s">
+        <v>609</v>
+      </c>
+      <c r="F81" t="s">
+        <v>610</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>612</v>
+      </c>
+      <c r="B82" t="s">
+        <v>552</v>
+      </c>
+      <c r="C82" t="s">
+        <v>553</v>
+      </c>
+      <c r="D82" t="s">
+        <v>219</v>
+      </c>
+      <c r="E82" t="s">
+        <v>613</v>
+      </c>
+      <c r="F82" t="s">
+        <v>555</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>615</v>
+      </c>
+      <c r="B83" t="s">
+        <v>616</v>
+      </c>
+      <c r="C83" t="s">
+        <v>327</v>
+      </c>
+      <c r="D83" t="s">
+        <v>219</v>
+      </c>
+      <c r="E83" t="s">
+        <v>617</v>
+      </c>
+      <c r="F83" t="s">
+        <v>226</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>619</v>
+      </c>
+      <c r="B84" t="s">
+        <v>620</v>
+      </c>
+      <c r="C84" t="s">
+        <v>621</v>
+      </c>
+      <c r="D84" t="s">
+        <v>219</v>
+      </c>
+      <c r="E84" t="s">
+        <v>622</v>
+      </c>
+      <c r="F84" t="s">
+        <v>623</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>625</v>
+      </c>
+      <c r="B85" t="s">
+        <v>626</v>
+      </c>
+      <c r="C85" t="s">
+        <v>218</v>
+      </c>
+      <c r="D85" t="s">
+        <v>219</v>
+      </c>
+      <c r="E85" t="s">
+        <v>627</v>
+      </c>
+      <c r="F85" t="s">
+        <v>628</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>630</v>
+      </c>
+      <c r="B86" t="s">
+        <v>631</v>
+      </c>
+      <c r="C86" t="s">
+        <v>478</v>
+      </c>
+      <c r="D86" t="s">
+        <v>219</v>
+      </c>
+      <c r="E86" t="s">
+        <v>226</v>
+      </c>
+      <c r="F86" t="s">
+        <v>226</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>633</v>
+      </c>
+      <c r="B87" t="s">
+        <v>490</v>
+      </c>
+      <c r="C87" t="s">
+        <v>260</v>
+      </c>
+      <c r="D87" t="s">
+        <v>219</v>
+      </c>
+      <c r="E87" t="s">
+        <v>634</v>
+      </c>
+      <c r="F87" t="s">
+        <v>492</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>636</v>
+      </c>
+      <c r="B88" t="s">
+        <v>265</v>
+      </c>
+      <c r="C88" t="s">
+        <v>327</v>
+      </c>
+      <c r="D88" t="s">
+        <v>219</v>
+      </c>
+      <c r="E88" t="s">
+        <v>637</v>
+      </c>
+      <c r="F88" t="s">
+        <v>226</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>639</v>
+      </c>
+      <c r="B89" t="s">
+        <v>640</v>
+      </c>
+      <c r="C89" t="s">
+        <v>641</v>
+      </c>
+      <c r="D89" t="s">
+        <v>219</v>
+      </c>
+      <c r="E89" t="s">
+        <v>464</v>
+      </c>
+      <c r="F89" t="s">
+        <v>642</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>644</v>
+      </c>
+      <c r="B90" t="s">
+        <v>645</v>
+      </c>
+      <c r="C90" t="s">
+        <v>646</v>
+      </c>
+      <c r="D90" t="s">
+        <v>219</v>
+      </c>
+      <c r="E90" t="s">
+        <v>647</v>
+      </c>
+      <c r="F90" t="s">
+        <v>648</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>650</v>
+      </c>
+      <c r="B91" t="s">
+        <v>490</v>
+      </c>
+      <c r="C91" t="s">
+        <v>260</v>
+      </c>
+      <c r="D91" t="s">
+        <v>219</v>
+      </c>
+      <c r="E91" t="s">
+        <v>651</v>
+      </c>
+      <c r="F91" t="s">
+        <v>492</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>653</v>
+      </c>
+      <c r="B92" t="s">
+        <v>654</v>
+      </c>
+      <c r="C92" t="s">
+        <v>655</v>
+      </c>
+      <c r="D92" t="s">
+        <v>219</v>
+      </c>
+      <c r="E92" t="s">
+        <v>656</v>
+      </c>
+      <c r="F92" t="s">
+        <v>657</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>659</v>
+      </c>
+      <c r="B93" t="s">
+        <v>552</v>
+      </c>
+      <c r="C93" t="s">
+        <v>553</v>
+      </c>
+      <c r="D93" t="s">
+        <v>219</v>
+      </c>
+      <c r="E93" t="s">
+        <v>660</v>
+      </c>
+      <c r="F93" t="s">
+        <v>555</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>662</v>
+      </c>
+      <c r="B94" t="s">
+        <v>282</v>
+      </c>
+      <c r="C94" t="s">
+        <v>283</v>
+      </c>
+      <c r="D94" t="s">
+        <v>219</v>
+      </c>
+      <c r="E94" t="s">
+        <v>663</v>
+      </c>
+      <c r="F94" t="s">
+        <v>288</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>665</v>
+      </c>
+      <c r="B95" t="s">
+        <v>666</v>
+      </c>
+      <c r="C95" t="s">
+        <v>248</v>
+      </c>
+      <c r="D95" t="s">
+        <v>249</v>
+      </c>
+      <c r="E95" t="s">
+        <v>667</v>
+      </c>
+      <c r="F95" t="s">
+        <v>262</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-19.xlsx
+++ b/docs/xlsx/jobs-2026-10-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="824">
   <si>
     <t>Title</t>
   </si>
@@ -631,6 +631,27 @@
     <t>https://www.conservationjobboard.com/job-listing-wildlife-health-coordinator---environmental-scientist-iii-greenwood-delaware/4573582810</t>
   </si>
   <si>
+    <t>2027 Future Talent Program – Social Impact Sustainability – Co-op</t>
+  </si>
+  <si>
+    <t>Merck</t>
+  </si>
+  <si>
+    <t>Rahway, New Jersey, United States</t>
+  </si>
+  <si>
+    <t>Internship</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Sustainability</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/2027-future-talent-program-social-impact-sustainability-co-op/</t>
+  </si>
+  <si>
     <t>Field Crew Leader (Backcountry, Forestry, Fuels, Trails)</t>
   </si>
   <si>
@@ -664,6 +685,27 @@
     <t>https://greenjobs.greenjobsearch.org/jobs/youth-crew-leader-2/</t>
   </si>
   <si>
+    <t>Accounting Manager</t>
+  </si>
+  <si>
+    <t>The Lenfest Institute for Journalism</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b358f5ddb7c14cb5911617091da27826-accounting-manager-the-lenfest-institute-for-journalism-philadelphia</t>
+  </si>
+  <si>
     <t>Advancement Director, Mid-Atlantic</t>
   </si>
   <si>
@@ -673,9 +715,6 @@
     <t>Remote</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 70000.00 - 80000.00/year</t>
   </si>
   <si>
@@ -694,9 +733,6 @@
     <t>New Haven, Connecticut</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Agriculture, Climate Change, Environment</t>
   </si>
   <si>
@@ -790,6 +826,24 @@
     <t>https://www.idealist.org/en/government-job/6c45c7a4d0d14e1f8b488e9bfada2112-attorney-represent-new-york-state-in-court-of-claims-3919-new-york-state-office-of-the-attorney-general-buffalo</t>
   </si>
   <si>
+    <t>AZ Water Association, Managing Director</t>
+  </si>
+  <si>
+    <t>Revolutionary HR Consulting</t>
+  </si>
+  <si>
+    <t>Chandler, Arizona</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Water Sanitation, Environment, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/bb0d8f5660dc4499af0980cba00aed19-az-water-association-managing-director-revolutionary-hr-consulting-chandler</t>
+  </si>
+  <si>
     <t>Bi-Lingual Case Manager</t>
   </si>
   <si>
@@ -886,6 +940,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/fed1bfe3bee34d12b57ad4186a59c8b2-case-manager-grand-ave-studios-geel-community-services-inc-the-bronx</t>
   </si>
   <si>
+    <t>Chief Financial Officer, Citizens For Citizens</t>
+  </si>
+  <si>
+    <t>Eos Transition Partners</t>
+  </si>
+  <si>
+    <t>Fall River, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Children Youth, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/5537bbc95d00472e996a3dd27c8f76e5-chief-financial-officer-citizens-for-citizens-eos-transition-partners-fall-river</t>
+  </si>
+  <si>
     <t>Chief Operations Officer</t>
   </si>
   <si>
@@ -901,6 +973,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/37da75dc627a42c4b9f938fa5ee9c13e-chief-operations-officer-oregon-state-bar-tigard</t>
   </si>
   <si>
+    <t>Client Services Coordinator</t>
+  </si>
+  <si>
+    <t>Miss Major &amp; Alexander L. Lee TGIJP Black Trans Cultural Center</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 29.81 - 32.21/hour</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Lgbtq, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3a2b00dd5b4e4e6ea23dc69ed943093b-client-services-coordinator-miss-major-alexander-l-lee-tgijp-black-trans-cultural-center-san-francisco</t>
+  </si>
+  <si>
     <t>Clinical Operations Director</t>
   </si>
   <si>
@@ -952,6 +1042,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/df38054cb3044867b25d0d41d3d84961-communications-associate-fair-elections-center-washington</t>
   </si>
   <si>
+    <t>Community Wellness Education and Engagement Manager (English/Spanish)</t>
+  </si>
+  <si>
+    <t>The GrowHaus</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 58500.00 - 58500.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2145090ac0dd48ac94c5e08fdb22d356-community-wellness-education-and-engagement-manager-englishspanish-the-growhaus-denver</t>
+  </si>
+  <si>
     <t>Construction Instructional Coordinator</t>
   </si>
   <si>
@@ -970,6 +1078,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/686c01f01c754068a4e92a447ea08bc8-construction-instructional-coordinator-texas-climate-jobs-project-austin</t>
   </si>
   <si>
+    <t>Country Representative / Regional Head</t>
+  </si>
+  <si>
+    <t>Global Culture Network</t>
+  </si>
+  <si>
+    <t>International Relations, Economic Development, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/b51a7149ab11496783bb13720812fc0d-country-representative-regional-head-global-culture-network-abuja</t>
+  </si>
+  <si>
+    <t>Creative Content &amp; Multimedia Production Specialist</t>
+  </si>
+  <si>
+    <t>Media, Arts Music, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/c351889508b9457996939094ee147966-creative-content-multimedia-production-specialist-global-culture-network-abuja</t>
+  </si>
+  <si>
     <t>Data Scientist: Use Data to Develop Legal Hypotheses (6463)</t>
   </si>
   <si>
@@ -1036,6 +1165,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/a030a19c384845079d3682ad9ebb3c53-development-manager-seatuck-environmental-association-west-sayville</t>
   </si>
   <si>
+    <t>Girls Educational &amp; Mentoring Services, Inc.</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Sexual Abuse Human Trafficking, Women, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f1139115bd7d42808d08724f9e6715a9-development-manager-girls-educational-mentoring-services-inc-new-york</t>
+  </si>
+  <si>
+    <t>Digital Fundraising &amp; Grant Writing Specialist</t>
+  </si>
+  <si>
+    <t>Civic Engagement, International Relations, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/b83ec44be3ed41b5b93d38ba079c473d-digital-fundraising-grant-writing-specialist-global-culture-network-abuja</t>
+  </si>
+  <si>
+    <t>Director of Communications</t>
+  </si>
+  <si>
+    <t>The Math Learning Center</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/bd7fd5129479472cb2a9f5d38967028c-director-of-communications-the-math-learning-center-portland</t>
+  </si>
+  <si>
     <t>Director of Community Programs</t>
   </si>
   <si>
@@ -1054,6 +1216,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/f1c2f6fda7bd4ad68febd32f4604d38c-director-of-community-programs-virginia-center-for-inclusive-communities-henrico</t>
   </si>
   <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Governors Action Alliance</t>
+  </si>
+  <si>
+    <t>USD 180000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Reproductive Health Rights, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c8eb11d75d314e538c56d06947ecfa2d-director-of-development-governors-action-alliance-washington</t>
+  </si>
+  <si>
     <t>Director of Development and Community Relations</t>
   </si>
   <si>
@@ -1108,15 +1285,27 @@
     <t>New Yorkers United for Child Care</t>
   </si>
   <si>
-    <t>USD 100000.00 - 110000.00/year</t>
-  </si>
-  <si>
     <t>Children Youth, Economic Development, Family</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/961423a266f645e6a024333420e7f065-director-of-organizing-and-campaigns-new-yorkers-united-for-child-care-new-york</t>
   </si>
   <si>
+    <t>Director of Organizing and Strategy, Downstate</t>
+  </si>
+  <si>
+    <t>The New York Immigration Coalition</t>
+  </si>
+  <si>
+    <t>USD 98400.00 - 98400.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/639f83c975634701ad14f8cfd0338f24-director-of-organizing-and-strategy-downstate-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
     <t>Director of Partner Success</t>
   </si>
   <si>
@@ -1168,6 +1357,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/f4214be840454cfa81e17d99fc42710b-director-of-youth-ministry-restoration-reston-methodist-church-reston</t>
   </si>
   <si>
+    <t>Director, Transformation Integration and Adaptation</t>
+  </si>
+  <si>
+    <t>Heifer International</t>
+  </si>
+  <si>
+    <t>Agriculture, Poverty, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8ab85afb6dc84e078e3d4ac65b623183-director-transformation-integration-and-adaptation-heifer-international-little-rock</t>
+  </si>
+  <si>
+    <t>Director/a del Departamento de Educación</t>
+  </si>
+  <si>
+    <t>Education for the Children Foundation</t>
+  </si>
+  <si>
+    <t>Jocotenango, SACATEPEQUEZ, GT</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a6e2c39810cc42ea8900069b368c3433-directora-del-departamento-de-educacion-education-for-the-children-foundation-jocotenango</t>
+  </si>
+  <si>
+    <t>Diversity and Inclusion/Equal Employment Specialist (6464)</t>
+  </si>
+  <si>
+    <t>USD 90836.00 - 90836.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/a4821732f81c4a84a8fac98b20c8967f-diversity-and-inclusionequal-employment-specialist-6464-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
     <t>Donor &amp; Member Relations Manager</t>
   </si>
   <si>
@@ -1192,9 +1417,6 @@
     <t>District 1199C Training &amp; Upgrading Fund</t>
   </si>
   <si>
-    <t>Philadelphia, Pennsylvania</t>
-  </si>
-  <si>
     <t>USD 55000.00 - 55000.00/year</t>
   </si>
   <si>
@@ -1204,6 +1426,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/f15bec4be7e5473b97f46fd83d07b690-ehs-ccp-disability-education-specialist-district-1199c-training-upgrading-fund-philadelphia</t>
   </si>
   <si>
+    <t>Environmental Program Educator</t>
+  </si>
+  <si>
+    <t>Solano Resource Conservation District</t>
+  </si>
+  <si>
+    <t>Dixon, California</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 26.09 - 29.65/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/377786bc0a664a37a3881cc697892a8a-environmental-program-educator-solano-resource-conservation-district-dixon</t>
+  </si>
+  <si>
     <t>Events &amp; Fundraising Manager - Boston</t>
   </si>
   <si>
@@ -1213,9 +1453,6 @@
     <t>Remote (Boston, Massachusetts)</t>
   </si>
   <si>
-    <t>Community Development, Education, Health Medicine</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/03c5477e9942489797c2e98957fc7feb-events-fundraising-manager-boston-national-ovarian-cancer-coalition-national-boston</t>
   </si>
   <si>
@@ -1282,6 +1519,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/895c08444eb74157a11c27726aa9430d-executive-director-shifting-gears-bellingham</t>
   </si>
   <si>
+    <t>Opportunity Council</t>
+  </si>
+  <si>
+    <t>USD 245000.00 - 295000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f052e4085dcf4172a52b073db2cba573-executive-director-opportunity-council-bellingham</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/9df387ee1220489da4856b33092609a6-executive-director-global-culture-network-abuja</t>
+  </si>
+  <si>
+    <t>Sobrato Early Academic Language (SEAL)</t>
+  </si>
+  <si>
+    <t>USD 300000.00 - 340000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/ea88072c58614d0e8a4ceba0f59875c7-executive-director-sobrato-early-academic-language-seal-milpitas</t>
+  </si>
+  <si>
+    <t>Experiential Facilitator</t>
+  </si>
+  <si>
+    <t>BELONG Partners</t>
+  </si>
+  <si>
+    <t>USD 40.36 - 40.36/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d98c48bbde5f4c5f8071c44313a332ca-experiential-facilitator-belong-partners-seattle</t>
+  </si>
+  <si>
     <t>Fact-Checker</t>
   </si>
   <si>
@@ -1378,6 +1654,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/a28e2621857f45b780dcc359d41baab7-general-counsel-american-rivers-arlington</t>
   </si>
   <si>
+    <t>Geopolitics Researcher [Remote - Part Time]</t>
+  </si>
+  <si>
+    <t>Center for Asia-Pacific Strategy and Taiwan Studies</t>
+  </si>
+  <si>
+    <t>USD 300.00/month</t>
+  </si>
+  <si>
+    <t>International Relations, Policy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dcfd429c2fbd40ab96d3abd349e2bdf8-geopolitics-researcher-remote-part-time-center-for-asia-pacific-strategy-and-taiwan-studies-taipei</t>
+  </si>
+  <si>
     <t>Grant Operations Coordinator</t>
   </si>
   <si>
@@ -1390,6 +1681,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/a703582b183a4c39abcd27e5880848a6-grant-operations-coordinator-animal-charity-evaluators-covina</t>
   </si>
   <si>
+    <t>Grants Development Manager</t>
+  </si>
+  <si>
+    <t>Ecumenical Project for International Cooperation</t>
+  </si>
+  <si>
+    <t>Agriculture, Climate Change, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0acae78e76964217b832b7e196ad6495-grants-development-manager-ecumenical-project-for-international-cooperation-allenspark</t>
+  </si>
+  <si>
     <t>HIV Outreach Nurse Case Manager</t>
   </si>
   <si>
@@ -1432,6 +1735,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/618cc506e9a146f1845b0cd45eb00663-individual-giving-engagement-coordinator-the-arc-of-northern-virginia-fairfax</t>
   </si>
   <si>
+    <t>IT Manager – Temporary</t>
+  </si>
+  <si>
+    <t>The Bronx Defenders</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac9e5156c6ed42d185734ff8d3c5b9e0-it-manager-temporary-the-bronx-defenders-bronx</t>
+  </si>
+  <si>
     <t>Judiciary Research Manager (Court Executive 2B)</t>
   </si>
   <si>
@@ -1456,6 +1780,15 @@
     <t>https://www.idealist.org/en/job/94788b17105945f7a8b2885e966c7fac-lead-organizer-seiu-healthcare-michigan-hcmi-seiu-detroit</t>
   </si>
   <si>
+    <t>LEGAL ADMINISTRATIVE ASSISTANT</t>
+  </si>
+  <si>
+    <t>Americans for Immigrant Justice</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/44366b48912b4ef39bcede3c6937c837-legal-administrative-assistant-americans-for-immigrant-justice-miami</t>
+  </si>
+  <si>
     <t>Legal Aid Staff Attorney - Worcester</t>
   </si>
   <si>
@@ -1498,6 +1831,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/0204a223ad0e44b2a330d4b189655da1-litigation-supervisor-family-defense-practice-bronx-center-for-family-representation-inc-new-york</t>
   </si>
   <si>
+    <t>Manager of Individual Giving and Events</t>
+  </si>
+  <si>
+    <t>USD 75800.00 - 75800.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/793148f6f9974f308110a4be4eeecfbb-manager-of-individual-giving-and-events-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
     <t>Manager, Corporate Partnerships</t>
   </si>
   <si>
@@ -1513,6 +1858,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/2c2eb5c87f5440d0a954e16e95b0cf6f-manager-corporate-partnerships-share-our-strength-washington</t>
   </si>
   <si>
+    <t>MANAGER, PROGRAMS, SUPPLIES &amp; INVENTORY – OSB &amp; FCRC</t>
+  </si>
+  <si>
+    <t>Assistance League of Los Angeles</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d765a96988c84252a8ed6fc64c0bd638-manager-programs-supplies-inventory-osb-fcrc-assistance-league-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
     <t>Marketing and Business Development Manager</t>
   </si>
   <si>
@@ -1543,6 +1903,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/a417226d3c9c41498c58c8f547529dfe-middle-school-inclusion-teacher-sy26-27-capital-city-public-charter-school-washington</t>
   </si>
   <si>
+    <t>Native Language Teacher</t>
+  </si>
+  <si>
+    <t>Civic Engagement, International Relations, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/192b63ea635f42549f7c44b1e36a80fb-native-language-teacher-global-culture-network-abuja</t>
+  </si>
+  <si>
     <t>NIH Clinical Center- Head of Bioethics Consultation Service</t>
   </si>
   <si>
@@ -1693,9 +2062,6 @@
     <t>Environmental Defense Fund</t>
   </si>
   <si>
-    <t>Full Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 68000.00 - 72000.00/year</t>
   </si>
   <si>
@@ -1714,9 +2080,6 @@
     <t>USD 55000.00 - 75000.00/year</t>
   </si>
   <si>
-    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/5018fbf573ba4dbfa76d59d1e99eda7e-plus-mas-media-digital-media-associate-studio-operations-associate-full-time-remote-accelerate-change-washington</t>
   </si>
   <si>
@@ -1741,9 +2104,6 @@
     <t>Masa</t>
   </si>
   <si>
-    <t>Bronx, NY</t>
-  </si>
-  <si>
     <t>Children Youth, Education, Urban Areas</t>
   </si>
   <si>
@@ -1774,12 +2134,36 @@
     <t>USD 55000.00 - 65000.00/year</t>
   </si>
   <si>
-    <t>Community Development, Economic Development, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/b6917af37b5849b4bb2d2b2aeee10117-program-manager-foundation-for-the-mid-south-inc-60507-jackson</t>
   </si>
   <si>
+    <t>Programs Manager</t>
+  </si>
+  <si>
+    <t>Peace of Mind, Inc.</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7981e93dbc184be2b34daf3e8cc836f0-programs-manager-peace-of-mind-inc-washington</t>
+  </si>
+  <si>
+    <t>Regional Advocacy Director - Southeast</t>
+  </si>
+  <si>
+    <t>American Families for Vaccines</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0639f7505e904b7c8dd2cad31360b7e0-regional-advocacy-director-southeast-american-families-for-vaccines-portland</t>
+  </si>
+  <si>
     <t>Regional Manager - Los Angeles</t>
   </si>
   <si>
@@ -1795,6 +2179,24 @@
     <t>https://www.idealist.org/en/government-job/f42edfbfa0a0437f87213fa5b09b2ce8-regional-manager-los-angeles-back-2-work-los-angeles</t>
   </si>
   <si>
+    <t>Resident Organizer &amp; Project Manager</t>
+  </si>
+  <si>
+    <t>East Bay Permanent Real Estate Cooperative Inc</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 76362.00 - 76362.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/cc84056000af47b18dcc547e822e3966-resident-organizer-project-manager-east-bay-permanent-real-estate-cooperative-inc-oakland</t>
+  </si>
+  <si>
     <t>Senior Advisor, Project Management</t>
   </si>
   <si>
@@ -1807,6 +2209,30 @@
     <t>https://www.idealist.org/en/consultant-job/83aab0e822cb43cf954c5948e12c9ecc-senior-advisor-project-management-bme-strategies-north-andover</t>
   </si>
   <si>
+    <t>Senior Communications Manager</t>
+  </si>
+  <si>
+    <t>Communications Access, Economic Development, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/619592c83bd240d8b616d45c4744402d-senior-communications-manager-global-culture-network-abuja</t>
+  </si>
+  <si>
+    <t>Senior Director of Network Strengthening</t>
+  </si>
+  <si>
+    <t>The One America Movement</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 137000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7727660c38c74386a60f4a8237087957-senior-director-of-network-strengthening-the-one-america-movement-washington</t>
+  </si>
+  <si>
     <t>Senior Director of Visitor Services and Business Development</t>
   </si>
   <si>
@@ -1825,9 +2251,6 @@
     <t>National Audubon Society</t>
   </si>
   <si>
-    <t>Oakland, California</t>
-  </si>
-  <si>
     <t>USD 186000.00 - 208000.00/year</t>
   </si>
   <si>
@@ -1852,6 +2275,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/027b884033c74d21b5ffc7b3d639c573-senior-ethics-professional-review-associate-national-association-of-social-workers-washington</t>
   </si>
   <si>
+    <t>Senior Manager, Communications</t>
+  </si>
+  <si>
+    <t>Susan Wojcicki Foundation</t>
+  </si>
+  <si>
+    <t>USD 155000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a6f67d9a7fcf4f96b5036d44250b74f4-senior-manager-communications-susan-wojcicki-foundation-san-francisco</t>
+  </si>
+  <si>
     <t>Senior Peer Specialist - Community Links</t>
   </si>
   <si>
@@ -1915,6 +2350,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/136144e1760c4538a01b962e7ae3671f-site-manager-greenlight-fund-detroit-greenlight-fund-detroit</t>
   </si>
   <si>
+    <t>Social &amp; Brand Marketing Manager</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce9cc596437647618627ba22a01e3dde-social-brand-marketing-manager-susan-wojcicki-foundation-san-francisco</t>
+  </si>
+  <si>
     <t>Social Work Supervisor (forensic), Bronx</t>
   </si>
   <si>
@@ -1981,9 +2425,6 @@
     <t>National Center for LGBTQ Rights</t>
   </si>
   <si>
-    <t>San Francisco, California</t>
-  </si>
-  <si>
     <t>USD 95143.00 - 153557.00/year</t>
   </si>
   <si>
@@ -1993,6 +2434,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/48b2c917e06b4a8e81fd586e09cce70c-staff-attorney-hogar-home-program-national-center-for-lgbtq-rights-san-francisco</t>
   </si>
   <si>
+    <t>Strategic Planning &amp; Organizational Development Manager</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/a9c5a78000764384ae9a59dbf3e68740-strategic-planning-organizational-development-manager-global-culture-network-abuja</t>
+  </si>
+  <si>
     <t>Supported Education Counselor - Full Time</t>
   </si>
   <si>
@@ -2000,6 +2450,21 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/d04b2907b8fc46fdb8d4ad53ec22d425-supported-education-counselor-full-time-baltic-street-wellness-solutions-kings-county</t>
+  </si>
+  <si>
+    <t>Vice President of Information Technology</t>
+  </si>
+  <si>
+    <t>Boys &amp; Girls Clubs of Metro Denver</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/15a8c2f0c1304edfa4a5c7ca5e468d48-vice-president-of-information-technology-boys-girls-clubs-of-metro-denver-denver</t>
   </si>
   <si>
     <t>Visiting Counselors- ATP</t>
@@ -3344,7 +3809,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3411,45 +3876,68 @@
         <v>212</v>
       </c>
       <c r="B3" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="D3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E3" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="F3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" t="s">
         <v>214</v>
       </c>
-      <c r="B4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C4" t="s">
-        <v>207</v>
-      </c>
       <c r="D4" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E4" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="F4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" t="s">
         <v>215</v>
+      </c>
+      <c r="E5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F5" t="s">
+        <v>217</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3458,6 +3946,7 @@
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
     <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3466,7 +3955,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3507,692 +3996,692 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C2" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D2" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E2" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="F2" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C3" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="D3" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E3" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F3" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B4" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C4" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="D4" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E4" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="F4" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B5" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C5" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D5" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E5" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="F5" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B6" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C6" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D6" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E6" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F6" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B7" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C7" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D7" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="E7" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F7" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B8" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C8" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D8" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="E8" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F8" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B9" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C9" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D9" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E9" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="F9" t="s">
-        <v>262</v>
+        <v>209</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B10" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C10" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D10" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E10" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="F10" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B11" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C11" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>226</v>
       </c>
       <c r="E11" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="F11" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B12" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C12" t="s">
-        <v>218</v>
+        <v>284</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>226</v>
       </c>
       <c r="E12" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="F12" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B13" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C13" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D13" t="s">
-        <v>219</v>
+        <v>291</v>
       </c>
       <c r="E13" t="s">
-        <v>284</v>
+        <v>209</v>
       </c>
       <c r="F13" t="s">
-        <v>226</v>
+        <v>292</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B14" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="C14" t="s">
-        <v>283</v>
+        <v>232</v>
       </c>
       <c r="D14" t="s">
-        <v>219</v>
+        <v>291</v>
       </c>
       <c r="E14" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="F14" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B15" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C15" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="D15" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E15" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="F15" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B16" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C16" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D16" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E16" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="F16" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B17" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="C17" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="D17" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E17" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="F17" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B18" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C18" t="s">
-        <v>218</v>
+        <v>316</v>
       </c>
       <c r="D18" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E18" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="F18" t="s">
-        <v>310</v>
+        <v>209</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B19" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C19" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="D19" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E19" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="F19" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B20" t="s">
-        <v>254</v>
+        <v>326</v>
       </c>
       <c r="C20" t="s">
-        <v>260</v>
+        <v>327</v>
       </c>
       <c r="D20" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E20" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="F20" t="s">
-        <v>226</v>
+        <v>329</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="B21" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="C21" t="s">
-        <v>260</v>
+        <v>333</v>
       </c>
       <c r="D21" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E21" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="F21" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>337</v>
       </c>
       <c r="B22" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="C22" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="D22" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E22" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="F22" t="s">
-        <v>226</v>
+        <v>340</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B23" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C23" t="s">
-        <v>303</v>
+        <v>344</v>
       </c>
       <c r="D23" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E23" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="F23" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="B24" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="C24" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="D24" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E24" t="s">
-        <v>267</v>
+        <v>351</v>
       </c>
       <c r="F24" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="B25" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="C25" t="s">
-        <v>342</v>
+        <v>232</v>
       </c>
       <c r="D25" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E25" t="s">
-        <v>343</v>
+        <v>209</v>
       </c>
       <c r="F25" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="B26" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C26" t="s">
-        <v>348</v>
+        <v>232</v>
       </c>
       <c r="D26" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E26" t="s">
-        <v>349</v>
+        <v>209</v>
       </c>
       <c r="F26" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="B27" t="s">
-        <v>353</v>
+        <v>266</v>
       </c>
       <c r="C27" t="s">
-        <v>354</v>
+        <v>278</v>
       </c>
       <c r="D27" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E27" t="s">
-        <v>226</v>
+        <v>362</v>
       </c>
       <c r="F27" t="s">
-        <v>355</v>
+        <v>209</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="B28" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C28" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="D28" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E28" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="F28" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>362</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C29" t="s">
-        <v>260</v>
+        <v>370</v>
       </c>
       <c r="D29" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E29" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="F29" t="s">
-        <v>365</v>
+        <v>209</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B30" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>333</v>
       </c>
       <c r="D30" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E30" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="F30" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B31" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C31" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="D31" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E31" t="s">
-        <v>375</v>
+        <v>285</v>
       </c>
       <c r="F31" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -4200,956 +4689,956 @@
         <v>378</v>
       </c>
       <c r="B32" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C32" t="s">
-        <v>380</v>
+        <v>278</v>
       </c>
       <c r="D32" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E32" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F32" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B33" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C33" t="s">
-        <v>354</v>
+        <v>232</v>
       </c>
       <c r="D33" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E33" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="F33" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B34" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C34" t="s">
-        <v>260</v>
+        <v>392</v>
       </c>
       <c r="D34" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E34" t="s">
-        <v>388</v>
+        <v>209</v>
       </c>
       <c r="F34" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B35" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C35" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D35" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E35" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F35" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B36" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C36" t="s">
-        <v>398</v>
+        <v>232</v>
       </c>
       <c r="D36" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E36" t="s">
-        <v>226</v>
+        <v>402</v>
       </c>
       <c r="F36" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B37" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C37" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D37" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E37" t="s">
-        <v>328</v>
+        <v>408</v>
       </c>
       <c r="F37" t="s">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B38" t="s">
-        <v>308</v>
+        <v>412</v>
       </c>
       <c r="C38" t="s">
-        <v>218</v>
+        <v>413</v>
       </c>
       <c r="D38" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="E38" t="s">
-        <v>406</v>
+        <v>209</v>
       </c>
       <c r="F38" t="s">
-        <v>310</v>
+        <v>414</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B39" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C39" t="s">
-        <v>242</v>
+        <v>278</v>
       </c>
       <c r="D39" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E39" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="F39" t="s">
-        <v>226</v>
+        <v>419</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>421</v>
       </c>
       <c r="B40" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="C40" t="s">
-        <v>413</v>
+        <v>278</v>
       </c>
       <c r="D40" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E40" t="s">
-        <v>414</v>
+        <v>227</v>
       </c>
       <c r="F40" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="B41" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="C41" t="s">
-        <v>418</v>
+        <v>278</v>
       </c>
       <c r="D41" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="E41" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="F41" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="B42" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="C42" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="D42" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E42" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="F42" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B43" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C43" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="D43" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E43" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="F43" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B44" t="s">
-        <v>391</v>
+        <v>442</v>
       </c>
       <c r="C44" t="s">
-        <v>392</v>
+        <v>443</v>
       </c>
       <c r="D44" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E44" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="F44" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="B45" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="C45" t="s">
-        <v>439</v>
+        <v>232</v>
       </c>
       <c r="D45" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E45" t="s">
-        <v>440</v>
+        <v>209</v>
       </c>
       <c r="F45" t="s">
-        <v>226</v>
+        <v>449</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="B46" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="C46" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="D46" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E46" t="s">
-        <v>445</v>
+        <v>209</v>
       </c>
       <c r="F46" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B47" t="s">
-        <v>449</v>
+        <v>266</v>
       </c>
       <c r="C47" t="s">
-        <v>450</v>
+        <v>278</v>
       </c>
       <c r="D47" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E47" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="F47" t="s">
-        <v>452</v>
+        <v>209</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B48" t="s">
-        <v>455</v>
+        <v>412</v>
       </c>
       <c r="C48" t="s">
-        <v>218</v>
+        <v>413</v>
       </c>
       <c r="D48" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="E48" t="s">
-        <v>456</v>
+        <v>209</v>
       </c>
       <c r="F48" t="s">
-        <v>360</v>
+        <v>414</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B49" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C49" t="s">
-        <v>303</v>
+        <v>278</v>
       </c>
       <c r="D49" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E49" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F49" t="s">
-        <v>461</v>
+        <v>250</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B50" t="s">
-        <v>423</v>
+        <v>466</v>
       </c>
       <c r="C50" t="s">
-        <v>327</v>
+        <v>225</v>
       </c>
       <c r="D50" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E50" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F50" t="s">
-        <v>425</v>
+        <v>468</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B51" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C51" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D51" t="s">
-        <v>219</v>
+        <v>473</v>
       </c>
       <c r="E51" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="F51" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B52" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C52" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D52" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E52" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="F52" t="s">
-        <v>475</v>
+        <v>346</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B53" t="s">
-        <v>438</v>
+        <v>481</v>
       </c>
       <c r="C53" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D53" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E53" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="F53" t="s">
-        <v>226</v>
+        <v>439</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B54" t="s">
-        <v>481</v>
+        <v>338</v>
       </c>
       <c r="C54" t="s">
-        <v>482</v>
+        <v>232</v>
       </c>
       <c r="D54" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="E54" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F54" t="s">
-        <v>484</v>
+        <v>340</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B55" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="C55" t="s">
-        <v>487</v>
+        <v>254</v>
       </c>
       <c r="D55" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E55" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="F55" t="s">
-        <v>484</v>
+        <v>209</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>489</v>
+        <v>78</v>
       </c>
       <c r="B56" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C56" t="s">
-        <v>260</v>
+        <v>492</v>
       </c>
       <c r="D56" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E56" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F56" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>494</v>
+        <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C57" t="s">
-        <v>327</v>
+        <v>497</v>
       </c>
       <c r="D57" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="E57" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F57" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>499</v>
+        <v>78</v>
       </c>
       <c r="B58" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C58" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="D58" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E58" t="s">
         <v>502</v>
       </c>
       <c r="F58" t="s">
+        <v>209</v>
+      </c>
+      <c r="H58" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>78</v>
+      </c>
+      <c r="B59" t="s">
+        <v>355</v>
+      </c>
+      <c r="C59" t="s">
+        <v>232</v>
+      </c>
+      <c r="D59" t="s">
+        <v>226</v>
+      </c>
+      <c r="E59" t="s">
+        <v>209</v>
+      </c>
+      <c r="F59" t="s">
+        <v>504</v>
+      </c>
+      <c r="H59" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="B59" t="s">
-        <v>506</v>
-      </c>
-      <c r="C59" t="s">
-        <v>327</v>
-      </c>
-      <c r="D59" t="s">
-        <v>219</v>
-      </c>
-      <c r="E59" t="s">
-        <v>507</v>
-      </c>
-      <c r="F59" t="s">
-        <v>232</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>509</v>
+        <v>78</v>
       </c>
       <c r="B60" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C60" t="s">
-        <v>511</v>
+        <v>232</v>
       </c>
       <c r="D60" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E60" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="F60" t="s">
-        <v>513</v>
+        <v>244</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="B61" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C61" t="s">
-        <v>517</v>
+        <v>254</v>
       </c>
       <c r="D61" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="E61" t="s">
-        <v>226</v>
+        <v>511</v>
       </c>
       <c r="F61" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="B62" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="C62" t="s">
-        <v>522</v>
+        <v>370</v>
       </c>
       <c r="D62" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E62" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="F62" t="s">
-        <v>262</v>
+        <v>517</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="B63" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C63" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="D63" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E63" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="F63" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B64" t="s">
+        <v>466</v>
+      </c>
+      <c r="C64" t="s">
+        <v>225</v>
+      </c>
+      <c r="D64" t="s">
+        <v>226</v>
+      </c>
+      <c r="E64" t="s">
         <v>526</v>
       </c>
-      <c r="C64" t="s">
+      <c r="F64" t="s">
         <v>527</v>
       </c>
-      <c r="D64" t="s">
-        <v>219</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="H64" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="F64" t="s">
-        <v>305</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>529</v>
+      </c>
+      <c r="B65" t="s">
+        <v>530</v>
+      </c>
+      <c r="C65" t="s">
+        <v>531</v>
+      </c>
+      <c r="D65" t="s">
+        <v>226</v>
+      </c>
+      <c r="E65" t="s">
         <v>532</v>
       </c>
-      <c r="B65" t="s">
+      <c r="F65" t="s">
+        <v>209</v>
+      </c>
+      <c r="H65" s="2" t="s">
         <v>533</v>
-      </c>
-      <c r="C65" t="s">
-        <v>534</v>
-      </c>
-      <c r="D65" t="s">
-        <v>249</v>
-      </c>
-      <c r="E65" t="s">
-        <v>535</v>
-      </c>
-      <c r="F65" t="s">
-        <v>536</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>534</v>
+      </c>
+      <c r="B66" t="s">
+        <v>535</v>
+      </c>
+      <c r="C66" t="s">
+        <v>536</v>
+      </c>
+      <c r="D66" t="s">
+        <v>226</v>
+      </c>
+      <c r="E66" t="s">
+        <v>537</v>
+      </c>
+      <c r="F66" t="s">
         <v>538</v>
       </c>
-      <c r="B66" t="s">
-        <v>368</v>
-      </c>
-      <c r="C66" t="s">
-        <v>218</v>
-      </c>
-      <c r="D66" t="s">
-        <v>219</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="H66" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="F66" t="s">
-        <v>370</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>540</v>
+      </c>
+      <c r="B67" t="s">
         <v>541</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>542</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
+        <v>226</v>
+      </c>
+      <c r="E67" t="s">
         <v>543</v>
       </c>
-      <c r="D67" t="s">
-        <v>219</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>544</v>
       </c>
-      <c r="F67" t="s">
+      <c r="H67" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B68" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C68" t="s">
-        <v>547</v>
+        <v>232</v>
       </c>
       <c r="D68" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="E68" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="F68" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="B69" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="C69" t="s">
-        <v>549</v>
+        <v>232</v>
       </c>
       <c r="D69" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="E69" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="F69" t="s">
-        <v>545</v>
+        <v>419</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B70" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C70" t="s">
-        <v>553</v>
+        <v>232</v>
       </c>
       <c r="D70" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="E70" t="s">
-        <v>554</v>
+        <v>209</v>
       </c>
       <c r="F70" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B71" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C71" t="s">
-        <v>260</v>
+        <v>333</v>
       </c>
       <c r="D71" t="s">
-        <v>559</v>
+        <v>226</v>
       </c>
       <c r="E71" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F71" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B72" t="s">
-        <v>564</v>
+        <v>515</v>
       </c>
       <c r="C72" t="s">
-        <v>218</v>
+        <v>370</v>
       </c>
       <c r="D72" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E72" t="s">
         <v>565</v>
       </c>
       <c r="F72" t="s">
+        <v>517</v>
+      </c>
+      <c r="H72" s="2" t="s">
         <v>566</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>567</v>
+      </c>
+      <c r="B73" t="s">
         <v>568</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>569</v>
       </c>
-      <c r="C73" t="s">
-        <v>327</v>
-      </c>
       <c r="D73" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E73" t="s">
         <v>570</v>
@@ -5172,59 +5661,59 @@
         <v>575</v>
       </c>
       <c r="D74" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="E74" t="s">
-        <v>406</v>
+        <v>577</v>
       </c>
       <c r="F74" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B75" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C75" t="s">
-        <v>218</v>
+        <v>582</v>
       </c>
       <c r="D75" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E75" t="s">
-        <v>580</v>
+        <v>209</v>
       </c>
       <c r="F75" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="B76" t="s">
-        <v>583</v>
+        <v>530</v>
       </c>
       <c r="C76" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D76" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E76" t="s">
-        <v>585</v>
+        <v>463</v>
       </c>
       <c r="F76" t="s">
-        <v>586</v>
+        <v>209</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>587</v>
@@ -5238,36 +5727,36 @@
         <v>589</v>
       </c>
       <c r="C77" t="s">
-        <v>248</v>
+        <v>413</v>
       </c>
       <c r="D77" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E77" t="s">
+        <v>209</v>
+      </c>
+      <c r="F77" t="s">
+        <v>578</v>
+      </c>
+      <c r="H77" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="F77" t="s">
-        <v>591</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>591</v>
+      </c>
+      <c r="B78" t="s">
+        <v>592</v>
+      </c>
+      <c r="C78" t="s">
         <v>593</v>
       </c>
-      <c r="B78" t="s">
+      <c r="D78" t="s">
+        <v>226</v>
+      </c>
+      <c r="E78" t="s">
         <v>594</v>
-      </c>
-      <c r="C78" t="s">
-        <v>218</v>
-      </c>
-      <c r="D78" t="s">
-        <v>219</v>
-      </c>
-      <c r="E78" t="s">
-        <v>226</v>
       </c>
       <c r="F78" t="s">
         <v>595</v>
@@ -5281,111 +5770,111 @@
         <v>597</v>
       </c>
       <c r="B79" t="s">
+        <v>592</v>
+      </c>
+      <c r="C79" t="s">
         <v>598</v>
       </c>
-      <c r="C79" t="s">
-        <v>575</v>
-      </c>
       <c r="D79" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E79" t="s">
+        <v>594</v>
+      </c>
+      <c r="F79" t="s">
+        <v>595</v>
+      </c>
+      <c r="H79" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="F79" t="s">
-        <v>226</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>600</v>
+      </c>
+      <c r="B80" t="s">
         <v>601</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
+        <v>278</v>
+      </c>
+      <c r="D80" t="s">
+        <v>226</v>
+      </c>
+      <c r="E80" t="s">
         <v>602</v>
       </c>
-      <c r="C80" t="s">
+      <c r="F80" t="s">
         <v>603</v>
       </c>
-      <c r="D80" t="s">
-        <v>219</v>
-      </c>
-      <c r="E80" t="s">
+      <c r="H80" s="2" t="s">
         <v>604</v>
-      </c>
-      <c r="F80" t="s">
-        <v>605</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>605</v>
+      </c>
+      <c r="B81" t="s">
+        <v>426</v>
+      </c>
+      <c r="C81" t="s">
+        <v>278</v>
+      </c>
+      <c r="D81" t="s">
+        <v>226</v>
+      </c>
+      <c r="E81" t="s">
+        <v>606</v>
+      </c>
+      <c r="F81" t="s">
         <v>607</v>
       </c>
-      <c r="B81" t="s">
+      <c r="H81" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="C81" t="s">
-        <v>327</v>
-      </c>
-      <c r="D81" t="s">
-        <v>219</v>
-      </c>
-      <c r="E81" t="s">
-        <v>609</v>
-      </c>
-      <c r="F81" t="s">
-        <v>610</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>609</v>
+      </c>
+      <c r="B82" t="s">
+        <v>610</v>
+      </c>
+      <c r="C82" t="s">
+        <v>370</v>
+      </c>
+      <c r="D82" t="s">
+        <v>226</v>
+      </c>
+      <c r="E82" t="s">
+        <v>611</v>
+      </c>
+      <c r="F82" t="s">
         <v>612</v>
       </c>
-      <c r="B82" t="s">
-        <v>552</v>
-      </c>
-      <c r="C82" t="s">
-        <v>553</v>
-      </c>
-      <c r="D82" t="s">
-        <v>219</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="H82" s="2" t="s">
         <v>613</v>
-      </c>
-      <c r="F82" t="s">
-        <v>555</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>614</v>
+      </c>
+      <c r="B83" t="s">
         <v>615</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
+        <v>260</v>
+      </c>
+      <c r="D83" t="s">
+        <v>226</v>
+      </c>
+      <c r="E83" t="s">
         <v>616</v>
       </c>
-      <c r="C83" t="s">
-        <v>327</v>
-      </c>
-      <c r="D83" t="s">
-        <v>219</v>
-      </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>617</v>
-      </c>
-      <c r="F83" t="s">
-        <v>226</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>618</v>
@@ -5402,7 +5891,7 @@
         <v>621</v>
       </c>
       <c r="D84" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E84" t="s">
         <v>622</v>
@@ -5422,249 +5911,1077 @@
         <v>626</v>
       </c>
       <c r="C85" t="s">
-        <v>218</v>
+        <v>370</v>
       </c>
       <c r="D85" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E85" t="s">
         <v>627</v>
       </c>
       <c r="F85" t="s">
+        <v>244</v>
+      </c>
+      <c r="H85" s="2" t="s">
         <v>628</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>629</v>
+      </c>
+      <c r="B86" t="s">
+        <v>355</v>
+      </c>
+      <c r="C86" t="s">
+        <v>232</v>
+      </c>
+      <c r="D86" t="s">
+        <v>226</v>
+      </c>
+      <c r="E86" t="s">
+        <v>209</v>
+      </c>
+      <c r="F86" t="s">
         <v>630</v>
       </c>
-      <c r="B86" t="s">
+      <c r="H86" s="2" t="s">
         <v>631</v>
-      </c>
-      <c r="C86" t="s">
-        <v>478</v>
-      </c>
-      <c r="D86" t="s">
-        <v>219</v>
-      </c>
-      <c r="E86" t="s">
-        <v>226</v>
-      </c>
-      <c r="F86" t="s">
-        <v>226</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>632</v>
+      </c>
+      <c r="B87" t="s">
         <v>633</v>
       </c>
-      <c r="B87" t="s">
-        <v>490</v>
-      </c>
       <c r="C87" t="s">
-        <v>260</v>
+        <v>634</v>
       </c>
       <c r="D87" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E87" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F87" t="s">
-        <v>492</v>
+        <v>636</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B88" t="s">
-        <v>265</v>
+        <v>639</v>
       </c>
       <c r="C88" t="s">
-        <v>327</v>
+        <v>640</v>
       </c>
       <c r="D88" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E88" t="s">
-        <v>637</v>
+        <v>209</v>
       </c>
       <c r="F88" t="s">
-        <v>226</v>
+        <v>641</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="B89" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C89" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="D89" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E89" t="s">
-        <v>464</v>
+        <v>646</v>
       </c>
       <c r="F89" t="s">
-        <v>642</v>
+        <v>280</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B90" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C90" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="D90" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E90" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="F90" t="s">
-        <v>648</v>
+        <v>335</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>653</v>
+      </c>
+      <c r="B91" t="s">
+        <v>649</v>
+      </c>
+      <c r="C91" t="s">
         <v>650</v>
       </c>
-      <c r="B91" t="s">
-        <v>490</v>
-      </c>
-      <c r="C91" t="s">
-        <v>260</v>
-      </c>
       <c r="D91" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E91" t="s">
         <v>651</v>
       </c>
       <c r="F91" t="s">
-        <v>492</v>
+        <v>335</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B92" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C92" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="D92" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="E92" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="F92" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B93" t="s">
-        <v>552</v>
+        <v>431</v>
       </c>
       <c r="C93" t="s">
-        <v>553</v>
+        <v>232</v>
       </c>
       <c r="D93" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E93" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="F93" t="s">
-        <v>555</v>
+        <v>433</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B94" t="s">
-        <v>282</v>
+        <v>665</v>
       </c>
       <c r="C94" t="s">
-        <v>283</v>
+        <v>666</v>
       </c>
       <c r="D94" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E94" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="F94" t="s">
-        <v>288</v>
+        <v>668</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>664</v>
+      </c>
+      <c r="B95" t="s">
         <v>665</v>
       </c>
-      <c r="B95" t="s">
-        <v>666</v>
-      </c>
       <c r="C95" t="s">
-        <v>248</v>
+        <v>670</v>
       </c>
       <c r="D95" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="E95" t="s">
         <v>667</v>
       </c>
       <c r="F95" t="s">
-        <v>262</v>
+        <v>668</v>
       </c>
       <c r="H95" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>664</v>
+      </c>
+      <c r="B96" t="s">
+        <v>665</v>
+      </c>
+      <c r="C96" t="s">
+        <v>672</v>
+      </c>
+      <c r="D96" t="s">
+        <v>226</v>
+      </c>
+      <c r="E96" t="s">
+        <v>667</v>
+      </c>
+      <c r="F96" t="s">
         <v>668</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>674</v>
+      </c>
+      <c r="B97" t="s">
+        <v>675</v>
+      </c>
+      <c r="C97" t="s">
+        <v>676</v>
+      </c>
+      <c r="D97" t="s">
+        <v>226</v>
+      </c>
+      <c r="E97" t="s">
+        <v>677</v>
+      </c>
+      <c r="F97" t="s">
+        <v>678</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>680</v>
+      </c>
+      <c r="B98" t="s">
+        <v>681</v>
+      </c>
+      <c r="C98" t="s">
+        <v>278</v>
+      </c>
+      <c r="D98" t="s">
+        <v>576</v>
+      </c>
+      <c r="E98" t="s">
+        <v>682</v>
+      </c>
+      <c r="F98" t="s">
+        <v>683</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>685</v>
+      </c>
+      <c r="B99" t="s">
+        <v>686</v>
+      </c>
+      <c r="C99" t="s">
+        <v>232</v>
+      </c>
+      <c r="D99" t="s">
+        <v>226</v>
+      </c>
+      <c r="E99" t="s">
+        <v>687</v>
+      </c>
+      <c r="F99" t="s">
+        <v>607</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>689</v>
+      </c>
+      <c r="B100" t="s">
+        <v>690</v>
+      </c>
+      <c r="C100" t="s">
+        <v>370</v>
+      </c>
+      <c r="D100" t="s">
+        <v>226</v>
+      </c>
+      <c r="E100" t="s">
+        <v>691</v>
+      </c>
+      <c r="F100" t="s">
+        <v>692</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>694</v>
+      </c>
+      <c r="B101" t="s">
+        <v>695</v>
+      </c>
+      <c r="C101" t="s">
+        <v>575</v>
+      </c>
+      <c r="D101" t="s">
+        <v>576</v>
+      </c>
+      <c r="E101" t="s">
+        <v>485</v>
+      </c>
+      <c r="F101" t="s">
+        <v>696</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>698</v>
+      </c>
+      <c r="B102" t="s">
+        <v>699</v>
+      </c>
+      <c r="C102" t="s">
+        <v>232</v>
+      </c>
+      <c r="D102" t="s">
+        <v>226</v>
+      </c>
+      <c r="E102" t="s">
+        <v>700</v>
+      </c>
+      <c r="F102" t="s">
+        <v>701</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>698</v>
+      </c>
+      <c r="B103" t="s">
+        <v>703</v>
+      </c>
+      <c r="C103" t="s">
+        <v>704</v>
+      </c>
+      <c r="D103" t="s">
+        <v>226</v>
+      </c>
+      <c r="E103" t="s">
+        <v>705</v>
+      </c>
+      <c r="F103" t="s">
+        <v>504</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>707</v>
+      </c>
+      <c r="B104" t="s">
+        <v>708</v>
+      </c>
+      <c r="C104" t="s">
+        <v>370</v>
+      </c>
+      <c r="D104" t="s">
+        <v>226</v>
+      </c>
+      <c r="E104" t="s">
+        <v>709</v>
+      </c>
+      <c r="F104" t="s">
+        <v>710</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>712</v>
+      </c>
+      <c r="B105" t="s">
+        <v>713</v>
+      </c>
+      <c r="C105" t="s">
+        <v>232</v>
+      </c>
+      <c r="D105" t="s">
+        <v>226</v>
+      </c>
+      <c r="E105" t="s">
+        <v>714</v>
+      </c>
+      <c r="F105" t="s">
+        <v>209</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>716</v>
+      </c>
+      <c r="B106" t="s">
+        <v>717</v>
+      </c>
+      <c r="C106" t="s">
+        <v>260</v>
+      </c>
+      <c r="D106" t="s">
+        <v>226</v>
+      </c>
+      <c r="E106" t="s">
+        <v>718</v>
+      </c>
+      <c r="F106" t="s">
+        <v>719</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>721</v>
+      </c>
+      <c r="B107" t="s">
+        <v>722</v>
+      </c>
+      <c r="C107" t="s">
+        <v>723</v>
+      </c>
+      <c r="D107" t="s">
+        <v>226</v>
+      </c>
+      <c r="E107" t="s">
+        <v>724</v>
+      </c>
+      <c r="F107" t="s">
+        <v>725</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>727</v>
+      </c>
+      <c r="B108" t="s">
+        <v>728</v>
+      </c>
+      <c r="C108" t="s">
+        <v>232</v>
+      </c>
+      <c r="D108" t="s">
+        <v>226</v>
+      </c>
+      <c r="E108" t="s">
+        <v>209</v>
+      </c>
+      <c r="F108" t="s">
+        <v>729</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>731</v>
+      </c>
+      <c r="B109" t="s">
+        <v>355</v>
+      </c>
+      <c r="C109" t="s">
+        <v>232</v>
+      </c>
+      <c r="D109" t="s">
+        <v>226</v>
+      </c>
+      <c r="E109" t="s">
+        <v>209</v>
+      </c>
+      <c r="F109" t="s">
+        <v>732</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>734</v>
+      </c>
+      <c r="B110" t="s">
+        <v>735</v>
+      </c>
+      <c r="C110" t="s">
+        <v>232</v>
+      </c>
+      <c r="D110" t="s">
+        <v>226</v>
+      </c>
+      <c r="E110" t="s">
+        <v>736</v>
+      </c>
+      <c r="F110" t="s">
+        <v>737</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>739</v>
+      </c>
+      <c r="B111" t="s">
+        <v>740</v>
+      </c>
+      <c r="C111" t="s">
+        <v>575</v>
+      </c>
+      <c r="D111" t="s">
+        <v>226</v>
+      </c>
+      <c r="E111" t="s">
+        <v>741</v>
+      </c>
+      <c r="F111" t="s">
+        <v>209</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>743</v>
+      </c>
+      <c r="B112" t="s">
+        <v>744</v>
+      </c>
+      <c r="C112" t="s">
+        <v>723</v>
+      </c>
+      <c r="D112" t="s">
+        <v>226</v>
+      </c>
+      <c r="E112" t="s">
+        <v>745</v>
+      </c>
+      <c r="F112" t="s">
+        <v>746</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>748</v>
+      </c>
+      <c r="B113" t="s">
+        <v>749</v>
+      </c>
+      <c r="C113" t="s">
+        <v>370</v>
+      </c>
+      <c r="D113" t="s">
+        <v>226</v>
+      </c>
+      <c r="E113" t="s">
+        <v>750</v>
+      </c>
+      <c r="F113" t="s">
+        <v>751</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>753</v>
+      </c>
+      <c r="B114" t="s">
+        <v>754</v>
+      </c>
+      <c r="C114" t="s">
+        <v>232</v>
+      </c>
+      <c r="D114" t="s">
+        <v>226</v>
+      </c>
+      <c r="E114" t="s">
+        <v>755</v>
+      </c>
+      <c r="F114" t="s">
+        <v>729</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>757</v>
+      </c>
+      <c r="B115" t="s">
+        <v>675</v>
+      </c>
+      <c r="C115" t="s">
+        <v>676</v>
+      </c>
+      <c r="D115" t="s">
+        <v>226</v>
+      </c>
+      <c r="E115" t="s">
+        <v>758</v>
+      </c>
+      <c r="F115" t="s">
+        <v>678</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>760</v>
+      </c>
+      <c r="B116" t="s">
+        <v>761</v>
+      </c>
+      <c r="C116" t="s">
+        <v>370</v>
+      </c>
+      <c r="D116" t="s">
+        <v>226</v>
+      </c>
+      <c r="E116" t="s">
+        <v>762</v>
+      </c>
+      <c r="F116" t="s">
+        <v>209</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>764</v>
+      </c>
+      <c r="B117" t="s">
+        <v>765</v>
+      </c>
+      <c r="C117" t="s">
+        <v>766</v>
+      </c>
+      <c r="D117" t="s">
+        <v>226</v>
+      </c>
+      <c r="E117" t="s">
+        <v>767</v>
+      </c>
+      <c r="F117" t="s">
+        <v>768</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>770</v>
+      </c>
+      <c r="B118" t="s">
+        <v>771</v>
+      </c>
+      <c r="C118" t="s">
+        <v>232</v>
+      </c>
+      <c r="D118" t="s">
+        <v>226</v>
+      </c>
+      <c r="E118" t="s">
+        <v>772</v>
+      </c>
+      <c r="F118" t="s">
+        <v>773</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>775</v>
+      </c>
+      <c r="B119" t="s">
+        <v>776</v>
+      </c>
+      <c r="C119" t="s">
+        <v>586</v>
+      </c>
+      <c r="D119" t="s">
+        <v>226</v>
+      </c>
+      <c r="E119" t="s">
+        <v>209</v>
+      </c>
+      <c r="F119" t="s">
+        <v>209</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>778</v>
+      </c>
+      <c r="B120" t="s">
+        <v>754</v>
+      </c>
+      <c r="C120" t="s">
+        <v>232</v>
+      </c>
+      <c r="D120" t="s">
+        <v>226</v>
+      </c>
+      <c r="E120" t="s">
+        <v>779</v>
+      </c>
+      <c r="F120" t="s">
+        <v>729</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>781</v>
+      </c>
+      <c r="B121" t="s">
+        <v>601</v>
+      </c>
+      <c r="C121" t="s">
+        <v>278</v>
+      </c>
+      <c r="D121" t="s">
+        <v>226</v>
+      </c>
+      <c r="E121" t="s">
+        <v>782</v>
+      </c>
+      <c r="F121" t="s">
+        <v>603</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>784</v>
+      </c>
+      <c r="B122" t="s">
+        <v>283</v>
+      </c>
+      <c r="C122" t="s">
+        <v>370</v>
+      </c>
+      <c r="D122" t="s">
+        <v>226</v>
+      </c>
+      <c r="E122" t="s">
+        <v>785</v>
+      </c>
+      <c r="F122" t="s">
+        <v>209</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>787</v>
+      </c>
+      <c r="B123" t="s">
+        <v>788</v>
+      </c>
+      <c r="C123" t="s">
+        <v>789</v>
+      </c>
+      <c r="D123" t="s">
+        <v>226</v>
+      </c>
+      <c r="E123" t="s">
+        <v>565</v>
+      </c>
+      <c r="F123" t="s">
+        <v>790</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>792</v>
+      </c>
+      <c r="B124" t="s">
+        <v>793</v>
+      </c>
+      <c r="C124" t="s">
+        <v>794</v>
+      </c>
+      <c r="D124" t="s">
+        <v>226</v>
+      </c>
+      <c r="E124" t="s">
+        <v>795</v>
+      </c>
+      <c r="F124" t="s">
+        <v>796</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>798</v>
+      </c>
+      <c r="B125" t="s">
+        <v>601</v>
+      </c>
+      <c r="C125" t="s">
+        <v>278</v>
+      </c>
+      <c r="D125" t="s">
+        <v>226</v>
+      </c>
+      <c r="E125" t="s">
+        <v>799</v>
+      </c>
+      <c r="F125" t="s">
+        <v>603</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>801</v>
+      </c>
+      <c r="B126" t="s">
+        <v>802</v>
+      </c>
+      <c r="C126" t="s">
+        <v>321</v>
+      </c>
+      <c r="D126" t="s">
+        <v>226</v>
+      </c>
+      <c r="E126" t="s">
+        <v>803</v>
+      </c>
+      <c r="F126" t="s">
+        <v>804</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>806</v>
+      </c>
+      <c r="B127" t="s">
+        <v>355</v>
+      </c>
+      <c r="C127" t="s">
+        <v>232</v>
+      </c>
+      <c r="D127" t="s">
+        <v>226</v>
+      </c>
+      <c r="E127" t="s">
+        <v>209</v>
+      </c>
+      <c r="F127" t="s">
+        <v>807</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>809</v>
+      </c>
+      <c r="B128" t="s">
+        <v>675</v>
+      </c>
+      <c r="C128" t="s">
+        <v>676</v>
+      </c>
+      <c r="D128" t="s">
+        <v>226</v>
+      </c>
+      <c r="E128" t="s">
+        <v>810</v>
+      </c>
+      <c r="F128" t="s">
+        <v>678</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>812</v>
+      </c>
+      <c r="B129" t="s">
+        <v>813</v>
+      </c>
+      <c r="C129" t="s">
+        <v>344</v>
+      </c>
+      <c r="D129" t="s">
+        <v>226</v>
+      </c>
+      <c r="E129" t="s">
+        <v>814</v>
+      </c>
+      <c r="F129" t="s">
+        <v>815</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>817</v>
+      </c>
+      <c r="B130" t="s">
+        <v>300</v>
+      </c>
+      <c r="C130" t="s">
+        <v>301</v>
+      </c>
+      <c r="D130" t="s">
+        <v>226</v>
+      </c>
+      <c r="E130" t="s">
+        <v>818</v>
+      </c>
+      <c r="F130" t="s">
+        <v>306</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>820</v>
+      </c>
+      <c r="B131" t="s">
+        <v>821</v>
+      </c>
+      <c r="C131" t="s">
+        <v>260</v>
+      </c>
+      <c r="D131" t="s">
+        <v>261</v>
+      </c>
+      <c r="E131" t="s">
+        <v>822</v>
+      </c>
+      <c r="F131" t="s">
+        <v>280</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>823</v>
       </c>
     </row>
   </sheetData>
@@ -5764,6 +7081,42 @@
     <hyperlink ref="H93" r:id="rId92"/>
     <hyperlink ref="H94" r:id="rId93"/>
     <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
